--- a/research/traditional_assets/database/data/sweden/sweden_retail_grocery_and_food.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_retail_grocery_and_food.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06924579469179407</v>
+        <v>0.06913887835472898</v>
       </c>
       <c r="C2">
-        <v>5258.964269273341</v>
+        <v>5223.023408783785</v>
       </c>
       <c r="D2">
-        <v>5230.86426927334</v>
+        <v>5251.123408783785</v>
       </c>
       <c r="E2">
-        <v>-1058.4</v>
+        <v>-1002.2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>56.2</v>
       </c>
       <c r="G2">
         <v>28.1</v>
@@ -1451,28 +1451,28 @@
         <v>323.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.82686</v>
       </c>
       <c r="N2">
-        <v>323.4</v>
+        <v>320.57314</v>
       </c>
       <c r="O2">
-        <v>66.6204</v>
+        <v>66.03806684</v>
       </c>
       <c r="P2">
-        <v>256.7796</v>
+        <v>254.53507316</v>
       </c>
       <c r="Q2">
-        <v>380.3796</v>
+        <v>378.13507316</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06924579469179407</v>
+        <v>0.06943383470174644</v>
       </c>
       <c r="T2">
-        <v>0.5414733185171841</v>
+        <v>0.5458160439202411</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>114.4025526555967</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06913887835472898</v>
+        <v>0.06903196201766387</v>
       </c>
       <c r="C3">
-        <v>5223.023408783785</v>
+        <v>5187.240085748515</v>
       </c>
       <c r="D3">
-        <v>5251.123408783785</v>
+        <v>5271.540085748515</v>
       </c>
       <c r="E3">
-        <v>-1002.2</v>
+        <v>-946.0000000000001</v>
       </c>
       <c r="F3">
-        <v>56.2</v>
+        <v>112.4</v>
       </c>
       <c r="G3">
         <v>28.1</v>
@@ -1533,28 +1533,28 @@
         <v>323.4</v>
       </c>
       <c r="M3">
-        <v>2.82686</v>
+        <v>5.65372</v>
       </c>
       <c r="N3">
-        <v>320.57314</v>
+        <v>317.74628</v>
       </c>
       <c r="O3">
-        <v>66.03806684</v>
+        <v>65.45573367999999</v>
       </c>
       <c r="P3">
-        <v>254.53507316</v>
+        <v>252.29054632</v>
       </c>
       <c r="Q3">
-        <v>378.13507316</v>
+        <v>375.89054632</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06943383470174644</v>
+        <v>0.06962571226292233</v>
       </c>
       <c r="T3">
-        <v>0.5458160439202411</v>
+        <v>0.55024739637234</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>114.4025526555967</v>
+        <v>57.20127632779833</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06903196201766387</v>
+        <v>0.06892504568059878</v>
       </c>
       <c r="C4">
-        <v>5187.240085748515</v>
+        <v>5151.616144884582</v>
       </c>
       <c r="D4">
-        <v>5271.540085748515</v>
+        <v>5292.116144884582</v>
       </c>
       <c r="E4">
-        <v>-946.0000000000001</v>
+        <v>-889.8000000000001</v>
       </c>
       <c r="F4">
-        <v>112.4</v>
+        <v>168.6</v>
       </c>
       <c r="G4">
         <v>28.1</v>
@@ -1615,28 +1615,28 @@
         <v>323.4</v>
       </c>
       <c r="M4">
-        <v>5.65372</v>
+        <v>8.48058</v>
       </c>
       <c r="N4">
-        <v>317.74628</v>
+        <v>314.91942</v>
       </c>
       <c r="O4">
-        <v>65.45573367999999</v>
+        <v>64.87340052</v>
       </c>
       <c r="P4">
-        <v>252.29054632</v>
+        <v>250.04601948</v>
       </c>
       <c r="Q4">
-        <v>375.89054632</v>
+        <v>373.64601948</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06962571226292233</v>
+        <v>0.06982154606247297</v>
       </c>
       <c r="T4">
-        <v>0.55024739637234</v>
+        <v>0.5547701169162349</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>57.20127632779833</v>
+        <v>38.13418421853223</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06892504568059878</v>
+        <v>0.06881812934353369</v>
       </c>
       <c r="C5">
-        <v>5151.616144884582</v>
+        <v>5116.153459823363</v>
       </c>
       <c r="D5">
-        <v>5292.116144884582</v>
+        <v>5312.853459823363</v>
       </c>
       <c r="E5">
-        <v>-889.8000000000001</v>
+        <v>-833.6000000000001</v>
       </c>
       <c r="F5">
-        <v>168.6</v>
+        <v>224.8</v>
       </c>
       <c r="G5">
         <v>28.1</v>
@@ -1697,28 +1697,28 @@
         <v>323.4</v>
       </c>
       <c r="M5">
-        <v>8.48058</v>
+        <v>11.30744</v>
       </c>
       <c r="N5">
-        <v>314.91942</v>
+        <v>312.09256</v>
       </c>
       <c r="O5">
-        <v>64.87340052</v>
+        <v>64.29106736</v>
       </c>
       <c r="P5">
-        <v>250.04601948</v>
+        <v>247.80149264</v>
       </c>
       <c r="Q5">
-        <v>373.64601948</v>
+        <v>371.40149264</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06982154606247297</v>
+        <v>0.0700214597328476</v>
       </c>
       <c r="T5">
-        <v>0.5547701169162349</v>
+        <v>0.5593870608047943</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>38.13418421853223</v>
+        <v>28.60063816389917</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06881812934353369</v>
+        <v>0.0687112130064686</v>
       </c>
       <c r="C6">
-        <v>5116.153459823363</v>
+        <v>5080.853933679289</v>
       </c>
       <c r="D6">
-        <v>5312.853459823363</v>
+        <v>5333.753933679289</v>
       </c>
       <c r="E6">
-        <v>-833.6000000000001</v>
+        <v>-777.4000000000001</v>
       </c>
       <c r="F6">
-        <v>224.8</v>
+        <v>281</v>
       </c>
       <c r="G6">
         <v>28.1</v>
@@ -1779,28 +1779,28 @@
         <v>323.4</v>
       </c>
       <c r="M6">
-        <v>11.30744</v>
+        <v>14.1343</v>
       </c>
       <c r="N6">
-        <v>312.09256</v>
+        <v>309.2657</v>
       </c>
       <c r="O6">
-        <v>64.29106736</v>
+        <v>63.7087342</v>
       </c>
       <c r="P6">
-        <v>247.80149264</v>
+        <v>245.5569658</v>
       </c>
       <c r="Q6">
-        <v>371.40149264</v>
+        <v>369.1569658</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0700214597328476</v>
+        <v>0.07022558211207221</v>
       </c>
       <c r="T6">
-        <v>0.5593870608047943</v>
+        <v>0.5641012035120601</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>28.60063816389917</v>
+        <v>22.88051053111933</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0687112130064686</v>
+        <v>0.06860429666940349</v>
       </c>
       <c r="C7">
-        <v>5080.853933679289</v>
+        <v>5045.719499632052</v>
       </c>
       <c r="D7">
-        <v>5333.753933679289</v>
+        <v>5354.819499632052</v>
       </c>
       <c r="E7">
-        <v>-777.4000000000001</v>
+        <v>-721.2</v>
       </c>
       <c r="F7">
-        <v>281</v>
+        <v>337.2</v>
       </c>
       <c r="G7">
         <v>28.1</v>
@@ -1861,28 +1861,28 @@
         <v>323.4</v>
       </c>
       <c r="M7">
-        <v>14.1343</v>
+        <v>16.96116</v>
       </c>
       <c r="N7">
-        <v>309.2657</v>
+        <v>306.43884</v>
       </c>
       <c r="O7">
-        <v>63.7087342</v>
+        <v>63.12640104</v>
       </c>
       <c r="P7">
-        <v>245.5569658</v>
+        <v>243.31243896</v>
       </c>
       <c r="Q7">
-        <v>369.1569658</v>
+        <v>366.91243896</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07022558211207221</v>
+        <v>0.07043404752064202</v>
       </c>
       <c r="T7">
-        <v>0.5641012035120601</v>
+        <v>0.568915647127991</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.88051053111933</v>
+        <v>19.06709210926611</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06860429666940349</v>
+        <v>0.0684973803323384</v>
       </c>
       <c r="C8">
-        <v>5045.719499632052</v>
+        <v>5010.75212152267</v>
       </c>
       <c r="D8">
-        <v>5354.819499632052</v>
+        <v>5376.052121522669</v>
       </c>
       <c r="E8">
-        <v>-721.2</v>
+        <v>-665.0000000000001</v>
       </c>
       <c r="F8">
-        <v>337.2</v>
+        <v>393.4</v>
       </c>
       <c r="G8">
         <v>28.1</v>
@@ -1943,28 +1943,28 @@
         <v>323.4</v>
       </c>
       <c r="M8">
-        <v>16.96116</v>
+        <v>19.78802</v>
       </c>
       <c r="N8">
-        <v>306.43884</v>
+        <v>303.61198</v>
       </c>
       <c r="O8">
-        <v>63.12640104</v>
+        <v>62.54406788</v>
       </c>
       <c r="P8">
-        <v>243.31243896</v>
+        <v>241.06791212</v>
       </c>
       <c r="Q8">
-        <v>366.91243896</v>
+        <v>364.66791212</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07043404752064202</v>
+        <v>0.07064699605627785</v>
       </c>
       <c r="T8">
-        <v>0.568915647127991</v>
+        <v>0.5738336271657701</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.06709210926611</v>
+        <v>16.34322180794238</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06849738033233839</v>
+        <v>0.06839046399527331</v>
       </c>
       <c r="C9">
-        <v>5010.752121522672</v>
+        <v>4975.953794463803</v>
       </c>
       <c r="D9">
-        <v>5376.052121522672</v>
+        <v>5397.453794463803</v>
       </c>
       <c r="E9">
-        <v>-665</v>
+        <v>-608.8000000000001</v>
       </c>
       <c r="F9">
-        <v>393.4</v>
+        <v>449.6</v>
       </c>
       <c r="G9">
         <v>28.1</v>
@@ -2025,28 +2025,28 @@
         <v>323.4</v>
       </c>
       <c r="M9">
-        <v>19.78802</v>
+        <v>22.61488</v>
       </c>
       <c r="N9">
-        <v>303.61198</v>
+        <v>300.78512</v>
       </c>
       <c r="O9">
-        <v>62.54406788</v>
+        <v>61.96173472000001</v>
       </c>
       <c r="P9">
-        <v>241.06791212</v>
+        <v>238.82338528</v>
       </c>
       <c r="Q9">
-        <v>364.66791212</v>
+        <v>362.42338528</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07064699605627785</v>
+        <v>0.07086457390790576</v>
       </c>
       <c r="T9">
-        <v>0.5738336271657701</v>
+        <v>0.5788585198130661</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.34322180794238</v>
+        <v>14.30031908194958</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06839046399527331</v>
+        <v>0.06839073765820822</v>
       </c>
       <c r="C10">
-        <v>4975.953794463803</v>
+        <v>4919.698797252454</v>
       </c>
       <c r="D10">
-        <v>5397.453794463803</v>
+        <v>5397.398797252454</v>
       </c>
       <c r="E10">
-        <v>-608.8000000000001</v>
+        <v>-552.6000000000001</v>
       </c>
       <c r="F10">
-        <v>449.6</v>
+        <v>505.8</v>
       </c>
       <c r="G10">
         <v>28.1</v>
@@ -2107,45 +2107,45 @@
         <v>323.4</v>
       </c>
       <c r="M10">
-        <v>22.61488</v>
+        <v>26.20044</v>
       </c>
       <c r="N10">
-        <v>300.78512</v>
+        <v>297.19956</v>
       </c>
       <c r="O10">
-        <v>61.96173472000001</v>
+        <v>61.22310936</v>
       </c>
       <c r="P10">
-        <v>238.82338528</v>
+        <v>235.97645064</v>
       </c>
       <c r="Q10">
-        <v>362.42338528</v>
+        <v>359.57645064</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07086457390790576</v>
+        <v>0.07108693369033869</v>
       </c>
       <c r="T10">
-        <v>0.5788585198130661</v>
+        <v>0.5839938496614016</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.206</v>
       </c>
       <c r="W10">
-        <v>0.0399382</v>
+        <v>0.0411292</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>14.30031908194958</v>
+        <v>12.34330415825078</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06839073765820822</v>
+        <v>0.06829573132114311</v>
       </c>
       <c r="C11">
-        <v>4919.698797252454</v>
+        <v>4882.659518358428</v>
       </c>
       <c r="D11">
-        <v>5397.398797252454</v>
+        <v>5416.559518358427</v>
       </c>
       <c r="E11">
-        <v>-552.6000000000001</v>
+        <v>-496.4000000000001</v>
       </c>
       <c r="F11">
-        <v>505.8</v>
+        <v>562</v>
       </c>
       <c r="G11">
         <v>28.1</v>
@@ -2189,28 +2189,28 @@
         <v>323.4</v>
       </c>
       <c r="M11">
-        <v>26.20044</v>
+        <v>29.1116</v>
       </c>
       <c r="N11">
-        <v>297.19956</v>
+        <v>294.2884</v>
       </c>
       <c r="O11">
-        <v>61.22310936</v>
+        <v>60.6234104</v>
       </c>
       <c r="P11">
-        <v>235.97645064</v>
+        <v>233.6649896</v>
       </c>
       <c r="Q11">
-        <v>359.57645064</v>
+        <v>357.2649896</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07108693369033869</v>
+        <v>0.07131423480127012</v>
       </c>
       <c r="T11">
-        <v>0.5839938496614016</v>
+        <v>0.5892432979508112</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.34330415825078</v>
+        <v>11.1089737424257</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06829573132114312</v>
+        <v>0.06820072498407802</v>
       </c>
       <c r="C12">
-        <v>4882.659518358424</v>
+        <v>4845.756764931698</v>
       </c>
       <c r="D12">
-        <v>5416.559518358424</v>
+        <v>5435.856764931697</v>
       </c>
       <c r="E12">
-        <v>-496.4000000000001</v>
+        <v>-440.2</v>
       </c>
       <c r="F12">
-        <v>562</v>
+        <v>618.2</v>
       </c>
       <c r="G12">
         <v>28.1</v>
@@ -2271,28 +2271,28 @@
         <v>323.4</v>
       </c>
       <c r="M12">
-        <v>29.1116</v>
+        <v>32.02276</v>
       </c>
       <c r="N12">
-        <v>294.2884</v>
+        <v>291.37724</v>
       </c>
       <c r="O12">
-        <v>60.6234104</v>
+        <v>60.02371144</v>
       </c>
       <c r="P12">
-        <v>233.6649896</v>
+        <v>231.35352856</v>
       </c>
       <c r="Q12">
-        <v>357.2649896</v>
+        <v>354.95352856</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07131423480127012</v>
+        <v>0.07154664380233486</v>
       </c>
       <c r="T12">
-        <v>0.5892432979508112</v>
+        <v>0.5946107113703198</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.1089737424257</v>
+        <v>10.09906703856882</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06820072498407802</v>
+        <v>0.06826769464701293</v>
       </c>
       <c r="C13">
-        <v>4845.756764931698</v>
+        <v>4775.939932398586</v>
       </c>
       <c r="D13">
-        <v>5435.856764931697</v>
+        <v>5422.239932398586</v>
       </c>
       <c r="E13">
-        <v>-440.2</v>
+        <v>-384.0000000000001</v>
       </c>
       <c r="F13">
-        <v>618.2</v>
+        <v>674.4</v>
       </c>
       <c r="G13">
         <v>28.1</v>
@@ -2353,45 +2353,45 @@
         <v>323.4</v>
       </c>
       <c r="M13">
-        <v>32.02276</v>
+        <v>36.0804</v>
       </c>
       <c r="N13">
-        <v>291.37724</v>
+        <v>287.3196</v>
       </c>
       <c r="O13">
-        <v>60.02371144</v>
+        <v>59.1878376</v>
       </c>
       <c r="P13">
-        <v>231.35352856</v>
+        <v>228.1317624</v>
       </c>
       <c r="Q13">
-        <v>354.95352856</v>
+        <v>351.7317624</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07154664380233486</v>
+        <v>0.07178433482615106</v>
       </c>
       <c r="T13">
-        <v>0.5946107113703198</v>
+        <v>0.6001001114584538</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.206</v>
       </c>
       <c r="W13">
-        <v>0.0411292</v>
+        <v>0.042479</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.09906703856882</v>
+        <v>8.963315262580238</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06826769464701293</v>
+        <v>0.06818618630994783</v>
       </c>
       <c r="C14">
-        <v>4775.939932398586</v>
+        <v>4736.321930132265</v>
       </c>
       <c r="D14">
-        <v>5422.239932398586</v>
+        <v>5438.821930132265</v>
       </c>
       <c r="E14">
-        <v>-384.0000000000001</v>
+        <v>-327.8000000000001</v>
       </c>
       <c r="F14">
-        <v>674.4</v>
+        <v>730.6</v>
       </c>
       <c r="G14">
         <v>28.1</v>
@@ -2435,28 +2435,28 @@
         <v>323.4</v>
       </c>
       <c r="M14">
-        <v>36.0804</v>
+        <v>39.0871</v>
       </c>
       <c r="N14">
-        <v>287.3196</v>
+        <v>284.3129</v>
       </c>
       <c r="O14">
-        <v>59.1878376</v>
+        <v>58.56845739999999</v>
       </c>
       <c r="P14">
-        <v>228.1317624</v>
+        <v>225.7444426</v>
       </c>
       <c r="Q14">
-        <v>351.7317624</v>
+        <v>349.3444426</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07178433482615106</v>
+        <v>0.07202749001143428</v>
       </c>
       <c r="T14">
-        <v>0.6001001114584538</v>
+        <v>0.6057157046520619</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.963315262580238</v>
+        <v>8.273829473150988</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06818618630994783</v>
+        <v>0.06810467797288274</v>
       </c>
       <c r="C15">
-        <v>4736.321930132265</v>
+        <v>4696.805659293334</v>
       </c>
       <c r="D15">
-        <v>5438.821930132265</v>
+        <v>5455.505659293333</v>
       </c>
       <c r="E15">
-        <v>-327.8000000000001</v>
+        <v>-271.6</v>
       </c>
       <c r="F15">
-        <v>730.6</v>
+        <v>786.8000000000001</v>
       </c>
       <c r="G15">
         <v>28.1</v>
@@ -2517,28 +2517,28 @@
         <v>323.4</v>
       </c>
       <c r="M15">
-        <v>39.0871</v>
+        <v>42.0938</v>
       </c>
       <c r="N15">
-        <v>284.3129</v>
+        <v>281.3062</v>
       </c>
       <c r="O15">
-        <v>58.56845739999999</v>
+        <v>57.9490772</v>
       </c>
       <c r="P15">
-        <v>225.7444426</v>
+        <v>223.3571228</v>
       </c>
       <c r="Q15">
-        <v>349.3444426</v>
+        <v>346.9571228</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07202749001143428</v>
+        <v>0.07227629996846829</v>
       </c>
       <c r="T15">
-        <v>0.6057157046520619</v>
+        <v>0.6114618930362191</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.273829473150988</v>
+        <v>7.682841653640203</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06810467797288274</v>
+        <v>0.06811844963581763</v>
       </c>
       <c r="C16">
-        <v>4696.805659293334</v>
+        <v>4637.779591202284</v>
       </c>
       <c r="D16">
-        <v>5455.505659293333</v>
+        <v>5452.679591202284</v>
       </c>
       <c r="E16">
-        <v>-271.6</v>
+        <v>-215.4</v>
       </c>
       <c r="F16">
-        <v>786.8000000000001</v>
+        <v>843.0000000000001</v>
       </c>
       <c r="G16">
         <v>28.1</v>
@@ -2599,45 +2599,45 @@
         <v>323.4</v>
       </c>
       <c r="M16">
-        <v>42.0938</v>
+        <v>45.77490000000001</v>
       </c>
       <c r="N16">
-        <v>281.3062</v>
+        <v>277.6251</v>
       </c>
       <c r="O16">
-        <v>57.9490772</v>
+        <v>57.1907706</v>
       </c>
       <c r="P16">
-        <v>223.3571228</v>
+        <v>220.4343294</v>
       </c>
       <c r="Q16">
-        <v>346.9571228</v>
+        <v>344.0343294</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07227629996846829</v>
+        <v>0.07253096427743251</v>
       </c>
       <c r="T16">
-        <v>0.6114618930362191</v>
+        <v>0.6173432858529447</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.206</v>
       </c>
       <c r="W16">
-        <v>0.042479</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.682841653640203</v>
+        <v>7.065007241960112</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06811844963581763</v>
+        <v>0.06804329329875254</v>
       </c>
       <c r="C17">
-        <v>4637.779591202284</v>
+        <v>4597.038053900344</v>
       </c>
       <c r="D17">
-        <v>5452.679591202284</v>
+        <v>5468.138053900344</v>
       </c>
       <c r="E17">
-        <v>-215.4000000000001</v>
+        <v>-159.2</v>
       </c>
       <c r="F17">
-        <v>843</v>
+        <v>899.2</v>
       </c>
       <c r="G17">
         <v>28.1</v>
@@ -2681,28 +2681,28 @@
         <v>323.4</v>
       </c>
       <c r="M17">
-        <v>45.7749</v>
+        <v>48.82656</v>
       </c>
       <c r="N17">
-        <v>277.6251</v>
+        <v>274.57344</v>
       </c>
       <c r="O17">
-        <v>57.1907706</v>
+        <v>56.56212864</v>
       </c>
       <c r="P17">
-        <v>220.4343294</v>
+        <v>218.01131136</v>
       </c>
       <c r="Q17">
-        <v>344.0343294</v>
+        <v>341.6113113600001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07253096427743251</v>
+        <v>0.07279169202232445</v>
       </c>
       <c r="T17">
-        <v>0.6173432858529447</v>
+        <v>0.6233647118319734</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.065007241960113</v>
+        <v>6.623444289337606</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06804329329875254</v>
+        <v>0.06796813696168744</v>
       </c>
       <c r="C18">
-        <v>4597.038053900344</v>
+        <v>4556.384415936449</v>
       </c>
       <c r="D18">
-        <v>5468.138053900344</v>
+        <v>5483.684415936448</v>
       </c>
       <c r="E18">
-        <v>-159.2</v>
+        <v>-103</v>
       </c>
       <c r="F18">
-        <v>899.2</v>
+        <v>955.4000000000001</v>
       </c>
       <c r="G18">
         <v>28.1</v>
@@ -2763,28 +2763,28 @@
         <v>323.4</v>
       </c>
       <c r="M18">
-        <v>48.82656</v>
+        <v>51.87822000000001</v>
       </c>
       <c r="N18">
-        <v>274.57344</v>
+        <v>271.52178</v>
       </c>
       <c r="O18">
-        <v>56.56212864</v>
+        <v>55.93348668</v>
       </c>
       <c r="P18">
-        <v>218.01131136</v>
+        <v>215.58829332</v>
       </c>
       <c r="Q18">
-        <v>341.6113113600001</v>
+        <v>339.18829332</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07279169202232445</v>
+        <v>0.07305870236347885</v>
       </c>
       <c r="T18">
-        <v>0.6233647118319734</v>
+        <v>0.6295312324129063</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.623444289337606</v>
+        <v>6.23382991937657</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06796813696168744</v>
+        <v>0.06803590062462235</v>
       </c>
       <c r="C19">
-        <v>4556.384415936449</v>
+        <v>4486.163345497539</v>
       </c>
       <c r="D19">
-        <v>5483.684415936448</v>
+        <v>5469.663345497539</v>
       </c>
       <c r="E19">
-        <v>-103</v>
+        <v>-46.79999999999995</v>
       </c>
       <c r="F19">
-        <v>955.4000000000001</v>
+        <v>1011.6</v>
       </c>
       <c r="G19">
         <v>28.1</v>
@@ -2845,45 +2845,45 @@
         <v>323.4</v>
       </c>
       <c r="M19">
-        <v>51.87822000000001</v>
+        <v>55.94148000000001</v>
       </c>
       <c r="N19">
-        <v>271.52178</v>
+        <v>267.45852</v>
       </c>
       <c r="O19">
-        <v>55.93348668</v>
+        <v>55.09645511999999</v>
       </c>
       <c r="P19">
-        <v>215.58829332</v>
+        <v>212.36206488</v>
       </c>
       <c r="Q19">
-        <v>339.18829332</v>
+        <v>335.96206488</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07305870236347885</v>
+        <v>0.07333222515197847</v>
       </c>
       <c r="T19">
-        <v>0.6295312324129063</v>
+        <v>0.6358481559348376</v>
       </c>
       <c r="U19">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.206</v>
       </c>
       <c r="W19">
-        <v>0.04311420000000001</v>
+        <v>0.0439082</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.23382991937657</v>
+        <v>5.781041188041502</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06803590062462235</v>
+        <v>0.06796868428755726</v>
       </c>
       <c r="C20">
-        <v>4486.16334549754</v>
+        <v>4443.870880054376</v>
       </c>
       <c r="D20">
-        <v>5469.663345497539</v>
+        <v>5483.570880054376</v>
       </c>
       <c r="E20">
-        <v>-46.80000000000018</v>
+        <v>9.399999999999864</v>
       </c>
       <c r="F20">
-        <v>1011.6</v>
+        <v>1067.8</v>
       </c>
       <c r="G20">
         <v>28.1</v>
@@ -2927,28 +2927,28 @@
         <v>323.4</v>
       </c>
       <c r="M20">
-        <v>55.94148</v>
+        <v>59.04934</v>
       </c>
       <c r="N20">
-        <v>267.45852</v>
+        <v>264.3506599999999</v>
       </c>
       <c r="O20">
-        <v>55.09645511999999</v>
+        <v>54.45623595999999</v>
       </c>
       <c r="P20">
-        <v>212.36206488</v>
+        <v>209.89442404</v>
       </c>
       <c r="Q20">
-        <v>335.96206488</v>
+        <v>333.49442404</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07333222515197847</v>
+        <v>0.07361250158957686</v>
       </c>
       <c r="T20">
-        <v>0.6358481559348376</v>
+        <v>0.6423210528770635</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.781041188041502</v>
+        <v>5.476775862355107</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06796868428755726</v>
+        <v>0.06790146795049215</v>
       </c>
       <c r="C21">
-        <v>4443.870880054376</v>
+        <v>4401.649319367279</v>
       </c>
       <c r="D21">
-        <v>5483.570880054376</v>
+        <v>5497.549319367278</v>
       </c>
       <c r="E21">
-        <v>9.399999999999864</v>
+        <v>65.59999999999991</v>
       </c>
       <c r="F21">
-        <v>1067.8</v>
+        <v>1124</v>
       </c>
       <c r="G21">
         <v>28.1</v>
@@ -3009,28 +3009,28 @@
         <v>323.4</v>
       </c>
       <c r="M21">
-        <v>59.04934</v>
+        <v>62.1572</v>
       </c>
       <c r="N21">
-        <v>264.3506599999999</v>
+        <v>261.2428</v>
       </c>
       <c r="O21">
-        <v>54.45623595999999</v>
+        <v>53.8160168</v>
       </c>
       <c r="P21">
-        <v>209.89442404</v>
+        <v>207.4267832</v>
       </c>
       <c r="Q21">
-        <v>333.49442404</v>
+        <v>331.0267832</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07361250158957686</v>
+        <v>0.07389978493811519</v>
       </c>
       <c r="T21">
-        <v>0.6423210528770635</v>
+        <v>0.6489557722428452</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.476775862355107</v>
+        <v>5.202937069237352</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06790146795049215</v>
+        <v>0.06783425161342707</v>
       </c>
       <c r="C22">
-        <v>4401.649319367279</v>
+        <v>4359.499207062385</v>
       </c>
       <c r="D22">
-        <v>5497.549319367278</v>
+        <v>5511.599207062384</v>
       </c>
       <c r="E22">
-        <v>65.59999999999991</v>
+        <v>121.8</v>
       </c>
       <c r="F22">
-        <v>1124</v>
+        <v>1180.2</v>
       </c>
       <c r="G22">
         <v>28.1</v>
@@ -3091,28 +3091,28 @@
         <v>323.4</v>
       </c>
       <c r="M22">
-        <v>62.1572</v>
+        <v>65.26506000000001</v>
       </c>
       <c r="N22">
-        <v>261.2428</v>
+        <v>258.13494</v>
       </c>
       <c r="O22">
-        <v>53.8160168</v>
+        <v>53.17579764</v>
       </c>
       <c r="P22">
-        <v>207.4267832</v>
+        <v>204.95914236</v>
       </c>
       <c r="Q22">
-        <v>331.0267832</v>
+        <v>328.55914236</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07389978493811519</v>
+        <v>0.07419434128281907</v>
       </c>
       <c r="T22">
-        <v>0.6489557722428452</v>
+        <v>0.6557584591875072</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.202937069237352</v>
+        <v>4.955178161178431</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06783425161342707</v>
+        <v>0.06776703527636196</v>
       </c>
       <c r="C23">
-        <v>4359.499207062385</v>
+        <v>4317.421092337403</v>
       </c>
       <c r="D23">
-        <v>5511.599207062384</v>
+        <v>5525.721092337402</v>
       </c>
       <c r="E23">
-        <v>121.8</v>
+        <v>178</v>
       </c>
       <c r="F23">
-        <v>1180.2</v>
+        <v>1236.4</v>
       </c>
       <c r="G23">
         <v>28.1</v>
@@ -3173,28 +3173,28 @@
         <v>323.4</v>
       </c>
       <c r="M23">
-        <v>65.26506000000001</v>
+        <v>68.37292000000001</v>
       </c>
       <c r="N23">
-        <v>258.13494</v>
+        <v>255.02708</v>
       </c>
       <c r="O23">
-        <v>53.17579764</v>
+        <v>52.53557848</v>
       </c>
       <c r="P23">
-        <v>204.95914236</v>
+        <v>202.49150152</v>
       </c>
       <c r="Q23">
-        <v>328.55914236</v>
+        <v>326.09150152</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07419434128281907</v>
+        <v>0.07449645035431021</v>
       </c>
       <c r="T23">
-        <v>0.6557584591875072</v>
+        <v>0.6627355740025451</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.955178161178431</v>
+        <v>4.729942790215775</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06776703527636196</v>
+        <v>0.06769981893929687</v>
       </c>
       <c r="C24">
-        <v>4317.421092337403</v>
+        <v>4275.415530033118</v>
       </c>
       <c r="D24">
-        <v>5525.721092337402</v>
+        <v>5539.915530033118</v>
       </c>
       <c r="E24">
-        <v>178</v>
+        <v>234.2</v>
       </c>
       <c r="F24">
-        <v>1236.4</v>
+        <v>1292.6</v>
       </c>
       <c r="G24">
         <v>28.1</v>
@@ -3255,28 +3255,28 @@
         <v>323.4</v>
       </c>
       <c r="M24">
-        <v>68.37292000000001</v>
+        <v>71.48078000000001</v>
       </c>
       <c r="N24">
-        <v>255.02708</v>
+        <v>251.91922</v>
       </c>
       <c r="O24">
-        <v>52.53557848</v>
+        <v>51.89535932</v>
       </c>
       <c r="P24">
-        <v>202.49150152</v>
+        <v>200.02386068</v>
       </c>
       <c r="Q24">
-        <v>326.09150152</v>
+        <v>323.62386068</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07449645035431021</v>
+        <v>0.07480640641467126</v>
       </c>
       <c r="T24">
-        <v>0.6627355740025451</v>
+        <v>0.6698939125790128</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.729942790215775</v>
+        <v>4.524293103684654</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06769981893929687</v>
+        <v>0.06810900260223178</v>
       </c>
       <c r="C25">
-        <v>4275.415530033118</v>
+        <v>4133.917891302331</v>
       </c>
       <c r="D25">
-        <v>5539.915530033118</v>
+        <v>5454.61789130233</v>
       </c>
       <c r="E25">
-        <v>234.2</v>
+        <v>290.4000000000001</v>
       </c>
       <c r="F25">
-        <v>1292.6</v>
+        <v>1348.8</v>
       </c>
       <c r="G25">
         <v>28.1</v>
@@ -3337,45 +3337,45 @@
         <v>323.4</v>
       </c>
       <c r="M25">
-        <v>71.48078000000001</v>
+        <v>77.96064000000001</v>
       </c>
       <c r="N25">
-        <v>251.91922</v>
+        <v>245.43936</v>
       </c>
       <c r="O25">
-        <v>51.89535932</v>
+        <v>50.56050816</v>
       </c>
       <c r="P25">
-        <v>200.02386068</v>
+        <v>194.87885184</v>
       </c>
       <c r="Q25">
-        <v>323.62386068</v>
+        <v>318.47885184</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07480640641467126</v>
+        <v>0.07512451921346286</v>
       </c>
       <c r="T25">
-        <v>0.6698939125790128</v>
+        <v>0.6772406284864401</v>
       </c>
       <c r="U25">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.206</v>
       </c>
       <c r="W25">
-        <v>0.0439082</v>
+        <v>0.04589320000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.524293103684654</v>
+        <v>4.148247115467496</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06810900260223178</v>
+        <v>0.06875638626516668</v>
       </c>
       <c r="C26">
-        <v>4133.917891302331</v>
+        <v>3948.003238883584</v>
       </c>
       <c r="D26">
-        <v>5454.61789130233</v>
+        <v>5324.903238883584</v>
       </c>
       <c r="E26">
-        <v>290.3999999999999</v>
+        <v>346.5999999999999</v>
       </c>
       <c r="F26">
-        <v>1348.8</v>
+        <v>1405</v>
       </c>
       <c r="G26">
         <v>28.1</v>
@@ -3419,45 +3419,45 @@
         <v>323.4</v>
       </c>
       <c r="M26">
-        <v>77.96064</v>
+        <v>86.12650000000001</v>
       </c>
       <c r="N26">
-        <v>245.43936</v>
+        <v>237.2735</v>
       </c>
       <c r="O26">
-        <v>50.56050816</v>
+        <v>48.87834099999999</v>
       </c>
       <c r="P26">
-        <v>194.87885184</v>
+        <v>188.395159</v>
       </c>
       <c r="Q26">
-        <v>318.47885184</v>
+        <v>311.995159</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07512451921346286</v>
+        <v>0.07545111502022224</v>
       </c>
       <c r="T26">
-        <v>0.6772406284864401</v>
+        <v>0.6847832568180654</v>
       </c>
       <c r="U26">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V26">
         <v>0.206</v>
       </c>
       <c r="W26">
-        <v>0.04589320000000001</v>
+        <v>0.04867220000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.148247115467496</v>
+        <v>3.754941858777495</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06875638626516668</v>
+        <v>0.06873680992810158</v>
       </c>
       <c r="C27">
-        <v>3948.003238883584</v>
+        <v>3895.635177466726</v>
       </c>
       <c r="D27">
-        <v>5324.903238883584</v>
+        <v>5328.735177466725</v>
       </c>
       <c r="E27">
-        <v>346.5999999999999</v>
+        <v>402.8</v>
       </c>
       <c r="F27">
-        <v>1405</v>
+        <v>1461.2</v>
       </c>
       <c r="G27">
         <v>28.1</v>
@@ -3501,28 +3501,28 @@
         <v>323.4</v>
       </c>
       <c r="M27">
-        <v>86.12650000000001</v>
+        <v>89.57156000000001</v>
       </c>
       <c r="N27">
-        <v>237.2735</v>
+        <v>233.82844</v>
       </c>
       <c r="O27">
-        <v>48.87834099999999</v>
+        <v>48.16865864</v>
       </c>
       <c r="P27">
-        <v>188.395159</v>
+        <v>185.65978136</v>
       </c>
       <c r="Q27">
-        <v>311.995159</v>
+        <v>309.25978136</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07545111502022224</v>
+        <v>0.07578653774067781</v>
       </c>
       <c r="T27">
-        <v>0.6847832568180654</v>
+        <v>0.6925297399694644</v>
       </c>
       <c r="U27">
         <v>0.0613</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.754941858777495</v>
+        <v>3.610521018055284</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06873680992810158</v>
+        <v>0.06931749759103649</v>
       </c>
       <c r="C28">
-        <v>3895.635177466726</v>
+        <v>3728.064926365101</v>
       </c>
       <c r="D28">
-        <v>5328.735177466725</v>
+        <v>5217.3649263651</v>
       </c>
       <c r="E28">
-        <v>402.8</v>
+        <v>459</v>
       </c>
       <c r="F28">
-        <v>1461.2</v>
+        <v>1517.4</v>
       </c>
       <c r="G28">
         <v>28.1</v>
@@ -3583,45 +3583,45 @@
         <v>323.4</v>
       </c>
       <c r="M28">
-        <v>89.57156000000001</v>
+        <v>97.26534000000001</v>
       </c>
       <c r="N28">
-        <v>233.82844</v>
+        <v>226.13466</v>
       </c>
       <c r="O28">
-        <v>48.16865864</v>
+        <v>46.58373996</v>
       </c>
       <c r="P28">
-        <v>185.65978136</v>
+        <v>179.55092004</v>
       </c>
       <c r="Q28">
-        <v>309.25978136</v>
+        <v>303.15092004</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07578653774067781</v>
+        <v>0.07613115012470752</v>
       </c>
       <c r="T28">
-        <v>0.6925297399694644</v>
+        <v>0.7004884555359703</v>
       </c>
       <c r="U28">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V28">
         <v>0.206</v>
       </c>
       <c r="W28">
-        <v>0.04867220000000001</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.610521018055284</v>
+        <v>3.324925405082632</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06931749759103649</v>
+        <v>0.06932015325397139</v>
       </c>
       <c r="C29">
-        <v>3728.064926365101</v>
+        <v>3671.366288654661</v>
       </c>
       <c r="D29">
-        <v>5217.3649263651</v>
+        <v>5216.866288654661</v>
       </c>
       <c r="E29">
-        <v>459</v>
+        <v>515.2</v>
       </c>
       <c r="F29">
-        <v>1517.4</v>
+        <v>1573.6</v>
       </c>
       <c r="G29">
         <v>28.1</v>
@@ -3665,28 +3665,28 @@
         <v>323.4</v>
       </c>
       <c r="M29">
-        <v>97.26534000000001</v>
+        <v>100.86776</v>
       </c>
       <c r="N29">
-        <v>226.13466</v>
+        <v>222.5322399999999</v>
       </c>
       <c r="O29">
-        <v>46.58373996</v>
+        <v>45.84164143999999</v>
       </c>
       <c r="P29">
-        <v>179.55092004</v>
+        <v>176.69059856</v>
       </c>
       <c r="Q29">
-        <v>303.15092004</v>
+        <v>300.29059856</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07613115012470752</v>
+        <v>0.07648533507496026</v>
       </c>
       <c r="T29">
-        <v>0.7004884555359703</v>
+        <v>0.708668246534879</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.324925405082632</v>
+        <v>3.206178069186823</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06932015325397139</v>
+        <v>0.0693228089169063</v>
       </c>
       <c r="C30">
-        <v>3671.366288654661</v>
+        <v>3614.667746247428</v>
       </c>
       <c r="D30">
-        <v>5216.866288654661</v>
+        <v>5216.367746247428</v>
       </c>
       <c r="E30">
-        <v>515.2</v>
+        <v>571.4000000000001</v>
       </c>
       <c r="F30">
-        <v>1573.6</v>
+        <v>1629.8</v>
       </c>
       <c r="G30">
         <v>28.1</v>
@@ -3747,28 +3747,28 @@
         <v>323.4</v>
       </c>
       <c r="M30">
-        <v>100.86776</v>
+        <v>104.47018</v>
       </c>
       <c r="N30">
-        <v>222.5322399999999</v>
+        <v>218.9298199999999</v>
       </c>
       <c r="O30">
-        <v>45.84164143999999</v>
+        <v>45.09954291999999</v>
       </c>
       <c r="P30">
-        <v>176.69059856</v>
+        <v>173.83027708</v>
       </c>
       <c r="Q30">
-        <v>300.29059856</v>
+        <v>297.43027708</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07648533507496026</v>
+        <v>0.07684949706606521</v>
       </c>
       <c r="T30">
-        <v>0.708668246534879</v>
+        <v>0.7170784541816444</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.206178069186823</v>
+        <v>3.095620204732106</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0693228089169063</v>
+        <v>0.0711834245798412</v>
       </c>
       <c r="C31">
-        <v>3614.667746247428</v>
+        <v>3231.128067640097</v>
       </c>
       <c r="D31">
-        <v>5216.367746247428</v>
+        <v>4889.028067640097</v>
       </c>
       <c r="E31">
-        <v>571.3999999999999</v>
+        <v>627.5999999999999</v>
       </c>
       <c r="F31">
-        <v>1629.8</v>
+        <v>1686</v>
       </c>
       <c r="G31">
         <v>28.1</v>
@@ -3829,45 +3829,45 @@
         <v>323.4</v>
       </c>
       <c r="M31">
-        <v>104.47018</v>
+        <v>121.2234</v>
       </c>
       <c r="N31">
-        <v>218.92982</v>
+        <v>202.1766</v>
       </c>
       <c r="O31">
-        <v>45.09954292</v>
+        <v>41.64837959999999</v>
       </c>
       <c r="P31">
-        <v>173.83027708</v>
+        <v>160.5282204</v>
       </c>
       <c r="Q31">
-        <v>297.43027708</v>
+        <v>284.1282204</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07684949706606521</v>
+        <v>0.07722406368548743</v>
       </c>
       <c r="T31">
-        <v>0.7170784541816444</v>
+        <v>0.7257289534754601</v>
       </c>
       <c r="U31">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V31">
         <v>0.206</v>
       </c>
       <c r="W31">
-        <v>0.05089540000000001</v>
+        <v>0.05708860000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>3.095620204732106</v>
+        <v>2.667801761046134</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0711834245798412</v>
+        <v>0.0712480122427761</v>
       </c>
       <c r="C32">
-        <v>3231.128067640097</v>
+        <v>3164.301307655473</v>
       </c>
       <c r="D32">
-        <v>4889.028067640097</v>
+        <v>4878.401307655472</v>
       </c>
       <c r="E32">
-        <v>627.5999999999999</v>
+        <v>683.8</v>
       </c>
       <c r="F32">
-        <v>1686</v>
+        <v>1742.2</v>
       </c>
       <c r="G32">
         <v>28.1</v>
@@ -3911,28 +3911,28 @@
         <v>323.4</v>
       </c>
       <c r="M32">
-        <v>121.2234</v>
+        <v>125.26418</v>
       </c>
       <c r="N32">
-        <v>202.1766</v>
+        <v>198.13582</v>
       </c>
       <c r="O32">
-        <v>41.64837959999999</v>
+        <v>40.81597892</v>
       </c>
       <c r="P32">
-        <v>160.5282204</v>
+        <v>157.31984108</v>
       </c>
       <c r="Q32">
-        <v>284.1282204</v>
+        <v>280.91984108</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07722406368548743</v>
+        <v>0.07760948730837117</v>
       </c>
       <c r="T32">
-        <v>0.7257289534754601</v>
+        <v>0.7346301918792416</v>
       </c>
       <c r="U32">
         <v>0.07190000000000001</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.667801761046134</v>
+        <v>2.581743639722065</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0712480122427761</v>
+        <v>0.07131259990571101</v>
       </c>
       <c r="C33">
-        <v>3164.301307655473</v>
+        <v>3097.520643990585</v>
       </c>
       <c r="D33">
-        <v>4878.401307655472</v>
+        <v>4867.820643990584</v>
       </c>
       <c r="E33">
-        <v>683.8</v>
+        <v>740</v>
       </c>
       <c r="F33">
-        <v>1742.2</v>
+        <v>1798.4</v>
       </c>
       <c r="G33">
         <v>28.1</v>
@@ -3993,28 +3993,28 @@
         <v>323.4</v>
       </c>
       <c r="M33">
-        <v>125.26418</v>
+        <v>129.30496</v>
       </c>
       <c r="N33">
-        <v>198.13582</v>
+        <v>194.09504</v>
       </c>
       <c r="O33">
-        <v>40.81597892</v>
+        <v>39.98357823999999</v>
       </c>
       <c r="P33">
-        <v>157.31984108</v>
+        <v>154.11146176</v>
       </c>
       <c r="Q33">
-        <v>280.91984108</v>
+        <v>277.71146176</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07760948730837117</v>
+        <v>0.07800624692016325</v>
       </c>
       <c r="T33">
-        <v>0.7346301918792416</v>
+        <v>0.7437932314125461</v>
       </c>
       <c r="U33">
         <v>0.07190000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.581743639722065</v>
+        <v>2.501064150980751</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07131259990571101</v>
+        <v>0.07239906556864591</v>
       </c>
       <c r="C34">
-        <v>3097.520643990585</v>
+        <v>2869.974707730818</v>
       </c>
       <c r="D34">
-        <v>4867.820643990584</v>
+        <v>4696.474707730818</v>
       </c>
       <c r="E34">
-        <v>740</v>
+        <v>796.2</v>
       </c>
       <c r="F34">
-        <v>1798.4</v>
+        <v>1854.6</v>
       </c>
       <c r="G34">
         <v>28.1</v>
@@ -4075,45 +4075,45 @@
         <v>323.4</v>
       </c>
       <c r="M34">
-        <v>129.30496</v>
+        <v>140.57868</v>
       </c>
       <c r="N34">
-        <v>194.09504</v>
+        <v>182.82132</v>
       </c>
       <c r="O34">
-        <v>39.98357823999999</v>
+        <v>37.66119191999999</v>
       </c>
       <c r="P34">
-        <v>154.11146176</v>
+        <v>145.16012808</v>
       </c>
       <c r="Q34">
-        <v>277.71146176</v>
+        <v>268.76012808</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07800624692016325</v>
+        <v>0.07841485010245658</v>
       </c>
       <c r="T34">
-        <v>0.7437932314125461</v>
+        <v>0.7532297945140088</v>
       </c>
       <c r="U34">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V34">
         <v>0.206</v>
       </c>
       <c r="W34">
-        <v>0.05708860000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.501064150980751</v>
+        <v>2.300491084423328</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07239906556864591</v>
+        <v>0.07249461923158082</v>
       </c>
       <c r="C35">
-        <v>2869.974707730818</v>
+        <v>2799.280310533723</v>
       </c>
       <c r="D35">
-        <v>4696.474707730818</v>
+        <v>4681.980310533723</v>
       </c>
       <c r="E35">
-        <v>796.2</v>
+        <v>852.4000000000001</v>
       </c>
       <c r="F35">
-        <v>1854.6</v>
+        <v>1910.8</v>
       </c>
       <c r="G35">
         <v>28.1</v>
@@ -4157,28 +4157,28 @@
         <v>323.4</v>
       </c>
       <c r="M35">
-        <v>140.57868</v>
+        <v>144.83864</v>
       </c>
       <c r="N35">
-        <v>182.82132</v>
+        <v>178.56136</v>
       </c>
       <c r="O35">
-        <v>37.66119191999999</v>
+        <v>36.78364015999999</v>
       </c>
       <c r="P35">
-        <v>145.16012808</v>
+        <v>141.77771984</v>
       </c>
       <c r="Q35">
-        <v>268.76012808</v>
+        <v>265.37771984</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07841485010245658</v>
+        <v>0.07883583519936488</v>
       </c>
       <c r="T35">
-        <v>0.7532297945140088</v>
+        <v>0.7629523140730917</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.300491084423328</v>
+        <v>2.232829581940289</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07249461923158082</v>
+        <v>0.07259017289451572</v>
       </c>
       <c r="C36">
-        <v>2799.280310533723</v>
+        <v>2728.675104135987</v>
       </c>
       <c r="D36">
-        <v>4681.980310533723</v>
+        <v>4667.575104135986</v>
       </c>
       <c r="E36">
-        <v>852.4000000000001</v>
+        <v>908.6000000000001</v>
       </c>
       <c r="F36">
-        <v>1910.8</v>
+        <v>1967</v>
       </c>
       <c r="G36">
         <v>28.1</v>
@@ -4239,28 +4239,28 @@
         <v>323.4</v>
       </c>
       <c r="M36">
-        <v>144.83864</v>
+        <v>149.0986</v>
       </c>
       <c r="N36">
-        <v>178.56136</v>
+        <v>174.3013999999999</v>
       </c>
       <c r="O36">
-        <v>36.78364015999999</v>
+        <v>35.90608839999999</v>
       </c>
       <c r="P36">
-        <v>141.77771984</v>
+        <v>138.3953116</v>
       </c>
       <c r="Q36">
-        <v>265.37771984</v>
+        <v>261.9953116</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07883583519936488</v>
+        <v>0.07926977368387034</v>
       </c>
       <c r="T36">
-        <v>0.7629523140730917</v>
+        <v>0.7729739880801464</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.232829581940289</v>
+        <v>2.169034451027708</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07259017289451572</v>
+        <v>0.07268572655745062</v>
       </c>
       <c r="C37">
-        <v>2728.675104135987</v>
+        <v>2658.158267813753</v>
       </c>
       <c r="D37">
-        <v>4667.575104135986</v>
+        <v>4653.258267813753</v>
       </c>
       <c r="E37">
-        <v>908.6000000000001</v>
+        <v>964.8000000000002</v>
       </c>
       <c r="F37">
-        <v>1967</v>
+        <v>2023.2</v>
       </c>
       <c r="G37">
         <v>28.1</v>
@@ -4321,28 +4321,28 @@
         <v>323.4</v>
       </c>
       <c r="M37">
-        <v>149.0986</v>
+        <v>153.35856</v>
       </c>
       <c r="N37">
-        <v>174.3013999999999</v>
+        <v>170.0414399999999</v>
       </c>
       <c r="O37">
-        <v>35.90608839999999</v>
+        <v>35.02853663999999</v>
       </c>
       <c r="P37">
-        <v>138.3953116</v>
+        <v>135.0129033599999</v>
       </c>
       <c r="Q37">
-        <v>261.9953116</v>
+        <v>258.61290336</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07926977368387034</v>
+        <v>0.0797172727460166</v>
       </c>
       <c r="T37">
-        <v>0.7729739880801464</v>
+        <v>0.7833088393999215</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.169034451027708</v>
+        <v>2.108783494054717</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07268572655745063</v>
+        <v>0.07278128022038553</v>
       </c>
       <c r="C38">
-        <v>2658.158267813752</v>
+        <v>2587.728990881989</v>
       </c>
       <c r="D38">
-        <v>4653.258267813751</v>
+        <v>4639.028990881989</v>
       </c>
       <c r="E38">
-        <v>964.7999999999997</v>
+        <v>1021</v>
       </c>
       <c r="F38">
-        <v>2023.2</v>
+        <v>2079.4</v>
       </c>
       <c r="G38">
         <v>28.1</v>
@@ -4403,28 +4403,28 @@
         <v>323.4</v>
       </c>
       <c r="M38">
-        <v>153.35856</v>
+        <v>157.61852</v>
       </c>
       <c r="N38">
-        <v>170.04144</v>
+        <v>165.78148</v>
       </c>
       <c r="O38">
-        <v>35.02853664</v>
+        <v>34.15098488</v>
       </c>
       <c r="P38">
-        <v>135.01290336</v>
+        <v>131.63049512</v>
       </c>
       <c r="Q38">
-        <v>258.61290336</v>
+        <v>255.23049512</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0797172727460166</v>
+        <v>0.08017897812759608</v>
       </c>
       <c r="T38">
-        <v>0.7833088393999215</v>
+        <v>0.7939717812377846</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.108783494054717</v>
+        <v>2.051789345566752</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07278128022038553</v>
+        <v>0.07716125788332043</v>
       </c>
       <c r="C39">
-        <v>2587.728990881989</v>
+        <v>1961.22251613784</v>
       </c>
       <c r="D39">
-        <v>4639.028990881989</v>
+        <v>4068.722516137839</v>
       </c>
       <c r="E39">
-        <v>1021</v>
+        <v>1077.2</v>
       </c>
       <c r="F39">
-        <v>2079.4</v>
+        <v>2135.6</v>
       </c>
       <c r="G39">
         <v>28.1</v>
@@ -4485,45 +4485,45 @@
         <v>323.4</v>
       </c>
       <c r="M39">
-        <v>157.61852</v>
+        <v>192.204</v>
       </c>
       <c r="N39">
-        <v>165.78148</v>
+        <v>131.196</v>
       </c>
       <c r="O39">
-        <v>34.15098488</v>
+        <v>27.026376</v>
       </c>
       <c r="P39">
-        <v>131.63049512</v>
+        <v>104.169624</v>
       </c>
       <c r="Q39">
-        <v>255.23049512</v>
+        <v>227.769624</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08017897812759608</v>
+        <v>0.08065557723116198</v>
       </c>
       <c r="T39">
-        <v>0.7939717812377846</v>
+        <v>0.8049786889413854</v>
       </c>
       <c r="U39">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V39">
         <v>0.206</v>
       </c>
       <c r="W39">
-        <v>0.06018520000000001</v>
+        <v>0.07146</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.051789345566752</v>
+        <v>1.682587251045764</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07716125788332043</v>
+        <v>0.07736955954625534</v>
       </c>
       <c r="C40">
-        <v>1961.22251613784</v>
+        <v>1881.372666453359</v>
       </c>
       <c r="D40">
-        <v>4068.722516137839</v>
+        <v>4045.072666453359</v>
       </c>
       <c r="E40">
-        <v>1077.2</v>
+        <v>1133.4</v>
       </c>
       <c r="F40">
-        <v>2135.6</v>
+        <v>2191.8</v>
       </c>
       <c r="G40">
         <v>28.1</v>
@@ -4567,28 +4567,28 @@
         <v>323.4</v>
       </c>
       <c r="M40">
-        <v>192.204</v>
+        <v>197.262</v>
       </c>
       <c r="N40">
-        <v>131.196</v>
+        <v>126.138</v>
       </c>
       <c r="O40">
-        <v>27.026376</v>
+        <v>25.984428</v>
       </c>
       <c r="P40">
-        <v>104.169624</v>
+        <v>100.153572</v>
       </c>
       <c r="Q40">
-        <v>227.769624</v>
+        <v>223.753572</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08065557723116198</v>
+        <v>0.08114780253484483</v>
       </c>
       <c r="T40">
-        <v>0.8049786889413854</v>
+        <v>0.8163464788647763</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.682587251045764</v>
+        <v>1.639443988198436</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07736955954625534</v>
+        <v>0.07757786120919025</v>
       </c>
       <c r="C41">
-        <v>1881.372666453359</v>
+        <v>1801.796162075758</v>
       </c>
       <c r="D41">
-        <v>4045.072666453359</v>
+        <v>4021.696162075758</v>
       </c>
       <c r="E41">
-        <v>1133.4</v>
+        <v>1189.6</v>
       </c>
       <c r="F41">
-        <v>2191.8</v>
+        <v>2248</v>
       </c>
       <c r="G41">
         <v>28.1</v>
@@ -4649,28 +4649,28 @@
         <v>323.4</v>
       </c>
       <c r="M41">
-        <v>197.262</v>
+        <v>202.32</v>
       </c>
       <c r="N41">
-        <v>126.138</v>
+        <v>121.08</v>
       </c>
       <c r="O41">
-        <v>25.984428</v>
+        <v>24.94248</v>
       </c>
       <c r="P41">
-        <v>100.153572</v>
+        <v>96.13751999999998</v>
       </c>
       <c r="Q41">
-        <v>223.753572</v>
+        <v>219.73752</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08114780253484483</v>
+        <v>0.08165643534865041</v>
       </c>
       <c r="T41">
-        <v>0.8163464788647763</v>
+        <v>0.8280931951189469</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.639443988198436</v>
+        <v>1.598457888493475</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07757786120919025</v>
+        <v>0.07778616287212514</v>
       </c>
       <c r="C42">
-        <v>1801.796162075758</v>
+        <v>1722.488291240803</v>
       </c>
       <c r="D42">
-        <v>4021.696162075758</v>
+        <v>3998.588291240803</v>
       </c>
       <c r="E42">
-        <v>1189.6</v>
+        <v>1245.8</v>
       </c>
       <c r="F42">
-        <v>2248</v>
+        <v>2304.2</v>
       </c>
       <c r="G42">
         <v>28.1</v>
@@ -4731,28 +4731,28 @@
         <v>323.4</v>
       </c>
       <c r="M42">
-        <v>202.32</v>
+        <v>207.378</v>
       </c>
       <c r="N42">
-        <v>121.08</v>
+        <v>116.022</v>
       </c>
       <c r="O42">
-        <v>24.94248</v>
+        <v>23.90053199999999</v>
       </c>
       <c r="P42">
-        <v>96.13751999999998</v>
+        <v>92.12146799999996</v>
       </c>
       <c r="Q42">
-        <v>219.73752</v>
+        <v>215.721468</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08165643534865041</v>
+        <v>0.0821823099527545</v>
       </c>
       <c r="T42">
-        <v>0.8280931951189469</v>
+        <v>0.8402381051444453</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.598457888493475</v>
+        <v>1.559471110725342</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07778616287212514</v>
+        <v>0.07799446453506005</v>
       </c>
       <c r="C43">
-        <v>1722.488291240803</v>
+        <v>1643.444449857056</v>
       </c>
       <c r="D43">
-        <v>3998.588291240803</v>
+        <v>3975.744449857056</v>
       </c>
       <c r="E43">
-        <v>1245.8</v>
+        <v>1302</v>
       </c>
       <c r="F43">
-        <v>2304.2</v>
+        <v>2360.4</v>
       </c>
       <c r="G43">
         <v>28.1</v>
@@ -4813,28 +4813,28 @@
         <v>323.4</v>
       </c>
       <c r="M43">
-        <v>207.378</v>
+        <v>212.436</v>
       </c>
       <c r="N43">
-        <v>116.022</v>
+        <v>110.964</v>
       </c>
       <c r="O43">
-        <v>23.90053199999999</v>
+        <v>22.858584</v>
       </c>
       <c r="P43">
-        <v>92.12146799999996</v>
+        <v>88.10541599999998</v>
       </c>
       <c r="Q43">
-        <v>215.721468</v>
+        <v>211.705416</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.0821823099527545</v>
+        <v>0.08272631816389664</v>
       </c>
       <c r="T43">
-        <v>0.8402381051444453</v>
+        <v>0.852801805170823</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.559471110725342</v>
+        <v>1.522340846184262</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07799446453506005</v>
+        <v>0.09892837289550746</v>
       </c>
       <c r="C44">
-        <v>1643.444449857056</v>
+        <v>137.1565670336363</v>
       </c>
       <c r="D44">
-        <v>3975.744449857056</v>
+        <v>2525.656567033636</v>
       </c>
       <c r="E44">
-        <v>1302</v>
+        <v>1358.2</v>
       </c>
       <c r="F44">
-        <v>2360.4</v>
+        <v>2416.6</v>
       </c>
       <c r="G44">
         <v>28.1</v>
@@ -4895,45 +4895,45 @@
         <v>323.4</v>
       </c>
       <c r="M44">
-        <v>212.436</v>
+        <v>354.75688</v>
       </c>
       <c r="N44">
-        <v>110.964</v>
+        <v>-31.35688000000005</v>
       </c>
       <c r="O44">
-        <v>22.858584</v>
+        <v>-6.45951728000001</v>
       </c>
       <c r="P44">
-        <v>88.10541599999998</v>
+        <v>-24.89736272000004</v>
       </c>
       <c r="Q44">
-        <v>211.705416</v>
+        <v>98.70263727999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08272631816389664</v>
+        <v>0.08361146771328959</v>
       </c>
       <c r="T44">
-        <v>0.8528018051708228</v>
+        <v>0.8732440580436396</v>
       </c>
       <c r="U44">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.206</v>
+        <v>0.1877917068162286</v>
       </c>
       <c r="W44">
-        <v>0.07146</v>
+        <v>0.1192321774393777</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y44">
-        <v>1.522340846184262</v>
+        <v>0.9116102272632456</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09892837289550746</v>
+        <v>0.09993837289550747</v>
       </c>
       <c r="C45">
-        <v>137.1565670336363</v>
+        <v>37.28032620980866</v>
       </c>
       <c r="D45">
-        <v>2525.656567033636</v>
+        <v>2481.980326209809</v>
       </c>
       <c r="E45">
-        <v>1358.2</v>
+        <v>1414.4</v>
       </c>
       <c r="F45">
-        <v>2416.6</v>
+        <v>2472.8</v>
       </c>
       <c r="G45">
         <v>28.1</v>
@@ -4977,37 +4977,37 @@
         <v>323.4</v>
       </c>
       <c r="M45">
-        <v>354.75688</v>
+        <v>363.0070400000001</v>
       </c>
       <c r="N45">
-        <v>-31.35688000000005</v>
+        <v>-39.6070400000001</v>
       </c>
       <c r="O45">
-        <v>-6.45951728000001</v>
+        <v>-8.15905024000002</v>
       </c>
       <c r="P45">
-        <v>-24.89736272000004</v>
+        <v>-31.44798976000008</v>
       </c>
       <c r="Q45">
-        <v>98.70263727999999</v>
+        <v>92.15201023999995</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08361146771328959</v>
+        <v>0.08428667249388407</v>
       </c>
       <c r="T45">
-        <v>0.8732440580436396</v>
+        <v>0.8888377019372762</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.1877917068162286</v>
+        <v>0.1835237134794961</v>
       </c>
       <c r="W45">
-        <v>0.1192321774393777</v>
+        <v>0.11985871886121</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.9116102272632456</v>
+        <v>0.8908918130072626</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09993837289550747</v>
+        <v>0.1009483728955075</v>
       </c>
       <c r="C46">
-        <v>37.28032620980866</v>
+        <v>-61.11100459639238</v>
       </c>
       <c r="D46">
-        <v>2481.980326209809</v>
+        <v>2439.788995403608</v>
       </c>
       <c r="E46">
-        <v>1414.4</v>
+        <v>1470.6</v>
       </c>
       <c r="F46">
-        <v>2472.8</v>
+        <v>2529</v>
       </c>
       <c r="G46">
         <v>28.1</v>
@@ -5059,37 +5059,37 @@
         <v>323.4</v>
       </c>
       <c r="M46">
-        <v>363.0070400000001</v>
+        <v>371.2572</v>
       </c>
       <c r="N46">
-        <v>-39.6070400000001</v>
+        <v>-47.85720000000003</v>
       </c>
       <c r="O46">
-        <v>-8.15905024000002</v>
+        <v>-9.858583200000007</v>
       </c>
       <c r="P46">
-        <v>-31.44798976000008</v>
+        <v>-37.99861680000003</v>
       </c>
       <c r="Q46">
-        <v>92.15201023999995</v>
+        <v>85.60138319999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08428667249388407</v>
+        <v>0.08498643017559104</v>
       </c>
       <c r="T46">
-        <v>0.8888377019372762</v>
+        <v>0.9049983874270447</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.1835237134794961</v>
+        <v>0.1794454087355074</v>
       </c>
       <c r="W46">
-        <v>0.11985871886121</v>
+        <v>0.1204574139976275</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8908918130072626</v>
+        <v>0.871094217162657</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1009483728955075</v>
+        <v>0.1019583728955075</v>
       </c>
       <c r="C47">
-        <v>-61.11100459639238</v>
+        <v>-158.0918858475879</v>
       </c>
       <c r="D47">
-        <v>2439.788995403608</v>
+        <v>2399.008114152412</v>
       </c>
       <c r="E47">
-        <v>1470.6</v>
+        <v>1526.8</v>
       </c>
       <c r="F47">
-        <v>2529</v>
+        <v>2585.2</v>
       </c>
       <c r="G47">
         <v>28.1</v>
@@ -5141,37 +5141,37 @@
         <v>323.4</v>
       </c>
       <c r="M47">
-        <v>371.2572</v>
+        <v>379.5073600000001</v>
       </c>
       <c r="N47">
-        <v>-47.85720000000003</v>
+        <v>-56.10736000000009</v>
       </c>
       <c r="O47">
-        <v>-9.858583200000007</v>
+        <v>-11.55811616000002</v>
       </c>
       <c r="P47">
-        <v>-37.99861680000003</v>
+        <v>-44.54924384000007</v>
       </c>
       <c r="Q47">
-        <v>85.60138319999999</v>
+        <v>79.05075615999996</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08498643017559104</v>
+        <v>0.08571210480847236</v>
       </c>
       <c r="T47">
-        <v>0.9049983874270447</v>
+        <v>0.9217576168238419</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.1794454087355074</v>
+        <v>0.1755444215890833</v>
       </c>
       <c r="W47">
-        <v>0.1204574139976275</v>
+        <v>0.1210300789107226</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.871094217162657</v>
+        <v>0.852157386354773</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1019583728955075</v>
+        <v>0.1029683728955075</v>
       </c>
       <c r="C48">
-        <v>-158.0918858475879</v>
+        <v>-253.7318814488567</v>
       </c>
       <c r="D48">
-        <v>2399.008114152412</v>
+        <v>2359.568118551143</v>
       </c>
       <c r="E48">
-        <v>1526.8</v>
+        <v>1583</v>
       </c>
       <c r="F48">
-        <v>2585.2</v>
+        <v>2641.4</v>
       </c>
       <c r="G48">
         <v>28.1</v>
@@ -5223,37 +5223,37 @@
         <v>323.4</v>
       </c>
       <c r="M48">
-        <v>379.5073600000001</v>
+        <v>387.7575200000001</v>
       </c>
       <c r="N48">
-        <v>-56.10736000000009</v>
+        <v>-64.35752000000008</v>
       </c>
       <c r="O48">
-        <v>-11.55811616000002</v>
+        <v>-13.25764912000002</v>
       </c>
       <c r="P48">
-        <v>-44.54924384000007</v>
+        <v>-51.09987088000006</v>
       </c>
       <c r="Q48">
-        <v>79.05075615999996</v>
+        <v>72.50012911999997</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08571210480847236</v>
+        <v>0.08646516338976429</v>
       </c>
       <c r="T48">
-        <v>0.9217576168238419</v>
+        <v>0.9391492699714616</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.1755444215890833</v>
+        <v>0.1718094338956985</v>
       </c>
       <c r="W48">
-        <v>0.1210300789107226</v>
+        <v>0.1215783751041115</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.852157386354773</v>
+        <v>0.8340263781344587</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1029683728955075</v>
+        <v>0.1039783728955075</v>
       </c>
       <c r="C49">
-        <v>-253.7318814488567</v>
+        <v>-348.096054737724</v>
       </c>
       <c r="D49">
-        <v>2359.568118551143</v>
+        <v>2321.403945262276</v>
       </c>
       <c r="E49">
-        <v>1583</v>
+        <v>1639.2</v>
       </c>
       <c r="F49">
-        <v>2641.4</v>
+        <v>2697.6</v>
       </c>
       <c r="G49">
         <v>28.1</v>
@@ -5305,37 +5305,37 @@
         <v>323.4</v>
       </c>
       <c r="M49">
-        <v>387.7575200000001</v>
+        <v>396.0076800000001</v>
       </c>
       <c r="N49">
-        <v>-64.35752000000008</v>
+        <v>-72.60768000000013</v>
       </c>
       <c r="O49">
-        <v>-13.25764912000002</v>
+        <v>-14.95718208000003</v>
       </c>
       <c r="P49">
-        <v>-51.09987088000006</v>
+        <v>-57.65049792000011</v>
       </c>
       <c r="Q49">
-        <v>72.50012911999997</v>
+        <v>65.94950207999992</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08646516338976429</v>
+        <v>0.08724718576264437</v>
       </c>
       <c r="T49">
-        <v>0.9391492699714616</v>
+        <v>0.9572098328555282</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.1718094338956985</v>
+        <v>0.1682300706895381</v>
       </c>
       <c r="W49">
-        <v>0.1215783751041115</v>
+        <v>0.1221038256227758</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8340263781344587</v>
+        <v>0.8166508285899907</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1039783728955075</v>
+        <v>0.1319575160087636</v>
       </c>
       <c r="C50">
-        <v>-348.0960547377231</v>
+        <v>-1122.587136676641</v>
       </c>
       <c r="D50">
-        <v>2321.403945262277</v>
+        <v>1603.112863323359</v>
       </c>
       <c r="E50">
-        <v>1639.2</v>
+        <v>1695.4</v>
       </c>
       <c r="F50">
-        <v>2697.6</v>
+        <v>2753.8</v>
       </c>
       <c r="G50">
         <v>28.1</v>
@@ -5387,45 +5387,45 @@
         <v>323.4</v>
       </c>
       <c r="M50">
-        <v>396.0076800000001</v>
+        <v>552.96304</v>
       </c>
       <c r="N50">
-        <v>-72.60768000000007</v>
+        <v>-229.56304</v>
       </c>
       <c r="O50">
-        <v>-14.95718208000002</v>
+        <v>-47.28998624</v>
       </c>
       <c r="P50">
-        <v>-57.65049792000006</v>
+        <v>-182.27305376</v>
       </c>
       <c r="Q50">
-        <v>65.94950207999997</v>
+        <v>-58.67305375999996</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08724718576264437</v>
+        <v>0.0890581955094729</v>
       </c>
       <c r="T50">
-        <v>0.9572098328555282</v>
+        <v>0.9990345383250091</v>
       </c>
       <c r="U50">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1682300706895381</v>
+        <v>0.12047893833917</v>
       </c>
       <c r="W50">
-        <v>0.1221038256227758</v>
+        <v>0.1766078291814947</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.8166508285899908</v>
+        <v>0.5848492152386894</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1319575160087636</v>
+        <v>0.1335075160087636</v>
       </c>
       <c r="C51">
-        <v>-1122.587136676641</v>
+        <v>-1205.803681100389</v>
       </c>
       <c r="D51">
-        <v>1603.112863323359</v>
+        <v>1576.096318899612</v>
       </c>
       <c r="E51">
-        <v>1695.4</v>
+        <v>1751.6</v>
       </c>
       <c r="F51">
-        <v>2753.8</v>
+        <v>2810</v>
       </c>
       <c r="G51">
         <v>28.1</v>
@@ -5469,37 +5469,37 @@
         <v>323.4</v>
       </c>
       <c r="M51">
-        <v>552.96304</v>
+        <v>564.248</v>
       </c>
       <c r="N51">
-        <v>-229.56304</v>
+        <v>-240.8480000000001</v>
       </c>
       <c r="O51">
-        <v>-47.28998624</v>
+        <v>-49.61468800000002</v>
       </c>
       <c r="P51">
-        <v>-182.27305376</v>
+        <v>-191.2333120000001</v>
       </c>
       <c r="Q51">
-        <v>-58.67305375999996</v>
+        <v>-67.63331200000005</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.0890581955094729</v>
+        <v>0.08992335941966237</v>
       </c>
       <c r="T51">
-        <v>0.9990345383250091</v>
+        <v>1.019015229091509</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.12047893833917</v>
+        <v>0.1180693595723866</v>
       </c>
       <c r="W51">
-        <v>0.1766078291814947</v>
+        <v>0.1770916725978648</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5848492152386894</v>
+        <v>0.5731522309339154</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1335075160087636</v>
+        <v>0.1350575160087636</v>
       </c>
       <c r="C52">
-        <v>-1205.803681100389</v>
+        <v>-1288.124721560916</v>
       </c>
       <c r="D52">
-        <v>1576.096318899612</v>
+        <v>1549.975278439085</v>
       </c>
       <c r="E52">
-        <v>1751.6</v>
+        <v>1807.8</v>
       </c>
       <c r="F52">
-        <v>2810</v>
+        <v>2866.2</v>
       </c>
       <c r="G52">
         <v>28.1</v>
@@ -5551,37 +5551,37 @@
         <v>323.4</v>
       </c>
       <c r="M52">
-        <v>564.248</v>
+        <v>575.5329600000001</v>
       </c>
       <c r="N52">
-        <v>-240.8480000000001</v>
+        <v>-252.1329600000001</v>
       </c>
       <c r="O52">
-        <v>-49.61468800000002</v>
+        <v>-51.93938976000003</v>
       </c>
       <c r="P52">
-        <v>-191.2333120000001</v>
+        <v>-200.1935702400001</v>
       </c>
       <c r="Q52">
-        <v>-67.63331200000005</v>
+        <v>-76.59357024000008</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08992335941966237</v>
+        <v>0.0908238361425126</v>
       </c>
       <c r="T52">
-        <v>1.019015229091509</v>
+        <v>1.039811458256642</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1180693595723866</v>
+        <v>0.1157542740905751</v>
       </c>
       <c r="W52">
-        <v>0.1770916725978648</v>
+        <v>0.1775565417626125</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5731522309339154</v>
+        <v>0.5619139518959955</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1350575160087636</v>
+        <v>0.1366075160087636</v>
       </c>
       <c r="C53">
-        <v>-1288.124721560916</v>
+        <v>-1369.594056413893</v>
       </c>
       <c r="D53">
-        <v>1549.975278439085</v>
+        <v>1524.705943586108</v>
       </c>
       <c r="E53">
-        <v>1807.8</v>
+        <v>1864</v>
       </c>
       <c r="F53">
-        <v>2866.2</v>
+        <v>2922.4</v>
       </c>
       <c r="G53">
         <v>28.1</v>
@@ -5633,37 +5633,37 @@
         <v>323.4</v>
       </c>
       <c r="M53">
-        <v>575.5329600000001</v>
+        <v>586.8179200000001</v>
       </c>
       <c r="N53">
-        <v>-252.1329600000001</v>
+        <v>-263.4179200000001</v>
       </c>
       <c r="O53">
-        <v>-51.93938976000003</v>
+        <v>-54.26409152000002</v>
       </c>
       <c r="P53">
-        <v>-200.1935702400001</v>
+        <v>-209.1538284800001</v>
       </c>
       <c r="Q53">
-        <v>-76.59357024000008</v>
+        <v>-85.55382848000005</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.0908238361425126</v>
+        <v>0.09176183272881497</v>
       </c>
       <c r="T53">
-        <v>1.039811458256642</v>
+        <v>1.061474196970322</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1157542740905751</v>
+        <v>0.113528230358064</v>
       </c>
       <c r="W53">
-        <v>0.1775565417626125</v>
+        <v>0.1780035313441007</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5619139518959955</v>
+        <v>0.5511079143595341</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1366075160087636</v>
+        <v>0.1381575160087636</v>
       </c>
       <c r="C54">
-        <v>-1369.594056413893</v>
+        <v>-1450.252673644319</v>
       </c>
       <c r="D54">
-        <v>1524.705943586108</v>
+        <v>1500.247326355682</v>
       </c>
       <c r="E54">
-        <v>1864</v>
+        <v>1920.2</v>
       </c>
       <c r="F54">
-        <v>2922.4</v>
+        <v>2978.6</v>
       </c>
       <c r="G54">
         <v>28.1</v>
@@ -5715,37 +5715,37 @@
         <v>323.4</v>
       </c>
       <c r="M54">
-        <v>586.8179200000001</v>
+        <v>598.1028800000001</v>
       </c>
       <c r="N54">
-        <v>-263.4179200000001</v>
+        <v>-274.7028800000002</v>
       </c>
       <c r="O54">
-        <v>-54.26409152000002</v>
+        <v>-56.58879328000004</v>
       </c>
       <c r="P54">
-        <v>-209.1538284800001</v>
+        <v>-218.1140867200001</v>
       </c>
       <c r="Q54">
-        <v>-85.55382848000005</v>
+        <v>-94.51408672000011</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09176183272881497</v>
+        <v>0.09273974406347059</v>
       </c>
       <c r="T54">
-        <v>1.061474196970322</v>
+        <v>1.084058754352669</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.113528230358064</v>
+        <v>0.1113861882758364</v>
       </c>
       <c r="W54">
-        <v>0.1780035313441007</v>
+        <v>0.178433653394212</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5511079143595341</v>
+        <v>0.5407096518244485</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1381575160087636</v>
+        <v>0.1397075160087636</v>
       </c>
       <c r="C55">
-        <v>-1450.252673644319</v>
+        <v>-1530.138972720876</v>
       </c>
       <c r="D55">
-        <v>1500.247326355682</v>
+        <v>1476.561027279124</v>
       </c>
       <c r="E55">
-        <v>1920.2</v>
+        <v>1976.4</v>
       </c>
       <c r="F55">
-        <v>2978.6</v>
+        <v>3034.8</v>
       </c>
       <c r="G55">
         <v>28.1</v>
@@ -5797,37 +5797,37 @@
         <v>323.4</v>
       </c>
       <c r="M55">
-        <v>598.1028800000001</v>
+        <v>609.3878400000001</v>
       </c>
       <c r="N55">
-        <v>-274.7028800000002</v>
+        <v>-285.9878400000001</v>
       </c>
       <c r="O55">
-        <v>-56.58879328000004</v>
+        <v>-58.91349504000003</v>
       </c>
       <c r="P55">
-        <v>-218.1140867200001</v>
+        <v>-227.0743449600001</v>
       </c>
       <c r="Q55">
-        <v>-94.51408672000011</v>
+        <v>-103.4743449600001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09273974406347059</v>
+        <v>0.09376017328224169</v>
       </c>
       <c r="T55">
-        <v>1.084058754352669</v>
+        <v>1.10762524901251</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1113861882758364</v>
+        <v>0.1093234810855431</v>
       </c>
       <c r="W55">
-        <v>0.178433653394212</v>
+        <v>0.1788478449980229</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5407096518244485</v>
+        <v>0.5306965101239958</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1397075160087636</v>
+        <v>0.1412575160087636</v>
       </c>
       <c r="C56">
-        <v>-1530.138972720876</v>
+        <v>-1609.288965760765</v>
       </c>
       <c r="D56">
-        <v>1476.561027279124</v>
+        <v>1453.611034239236</v>
       </c>
       <c r="E56">
-        <v>1976.4</v>
+        <v>2032.6</v>
       </c>
       <c r="F56">
-        <v>3034.8</v>
+        <v>3091</v>
       </c>
       <c r="G56">
         <v>28.1</v>
@@ -5879,37 +5879,37 @@
         <v>323.4</v>
       </c>
       <c r="M56">
-        <v>609.3878400000001</v>
+        <v>620.6728000000002</v>
       </c>
       <c r="N56">
-        <v>-285.9878400000001</v>
+        <v>-297.2728000000002</v>
       </c>
       <c r="O56">
-        <v>-58.91349504000003</v>
+        <v>-61.23819680000005</v>
       </c>
       <c r="P56">
-        <v>-227.0743449600001</v>
+        <v>-236.0346032000001</v>
       </c>
       <c r="Q56">
-        <v>-103.4743449600001</v>
+        <v>-112.4346032000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09376017328224169</v>
+        <v>0.09482595491073596</v>
       </c>
       <c r="T56">
-        <v>1.10762524901251</v>
+        <v>1.132239143435011</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1093234810855431</v>
+        <v>0.1073357814294423</v>
       </c>
       <c r="W56">
-        <v>0.1788478449980229</v>
+        <v>0.179246975088968</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5306965101239958</v>
+        <v>0.5210474826671958</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1412575160087636</v>
+        <v>0.1428075160087636</v>
       </c>
       <c r="C57">
-        <v>-1609.288965760765</v>
+        <v>-1687.736460221591</v>
       </c>
       <c r="D57">
-        <v>1453.611034239236</v>
+        <v>1431.363539778409</v>
       </c>
       <c r="E57">
-        <v>2032.6</v>
+        <v>2088.8</v>
       </c>
       <c r="F57">
-        <v>3091</v>
+        <v>3147.2</v>
       </c>
       <c r="G57">
         <v>28.1</v>
@@ -5961,37 +5961,37 @@
         <v>323.4</v>
       </c>
       <c r="M57">
-        <v>620.6728000000002</v>
+        <v>631.9577600000001</v>
       </c>
       <c r="N57">
-        <v>-297.2728000000002</v>
+        <v>-308.5577600000001</v>
       </c>
       <c r="O57">
-        <v>-61.23819680000005</v>
+        <v>-63.56289856000004</v>
       </c>
       <c r="P57">
-        <v>-236.0346032000001</v>
+        <v>-244.9948614400001</v>
       </c>
       <c r="Q57">
-        <v>-112.4346032000001</v>
+        <v>-121.3948614400001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09482595491073596</v>
+        <v>0.09594018115870723</v>
       </c>
       <c r="T57">
-        <v>1.132239143435011</v>
+        <v>1.157971851240352</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1073357814294423</v>
+        <v>0.1054190710467738</v>
       </c>
       <c r="W57">
-        <v>0.179246975088968</v>
+        <v>0.1796318505338078</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5210474826671958</v>
+        <v>0.5117430633338531</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1428075160087636</v>
+        <v>0.1443575160087636</v>
       </c>
       <c r="C58">
-        <v>-1687.736460221591</v>
+        <v>-1765.513225069572</v>
       </c>
       <c r="D58">
-        <v>1431.363539778409</v>
+        <v>1409.786774930428</v>
       </c>
       <c r="E58">
-        <v>2088.8</v>
+        <v>2145</v>
       </c>
       <c r="F58">
-        <v>3147.2</v>
+        <v>3203.400000000001</v>
       </c>
       <c r="G58">
         <v>28.1</v>
@@ -6043,37 +6043,37 @@
         <v>323.4</v>
       </c>
       <c r="M58">
-        <v>631.9577600000001</v>
+        <v>643.2427200000001</v>
       </c>
       <c r="N58">
-        <v>-308.5577600000001</v>
+        <v>-319.8427200000001</v>
       </c>
       <c r="O58">
-        <v>-63.56289856000004</v>
+        <v>-65.88760032000003</v>
       </c>
       <c r="P58">
-        <v>-244.9948614400001</v>
+        <v>-253.9551196800001</v>
       </c>
       <c r="Q58">
-        <v>-121.3948614400001</v>
+        <v>-130.35511968</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09594018115870723</v>
+        <v>0.09710623188332834</v>
       </c>
       <c r="T58">
-        <v>1.157971851240352</v>
+        <v>1.184901429176174</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1054190710467738</v>
+        <v>0.1035696136599882</v>
       </c>
       <c r="W58">
-        <v>0.1796318505338078</v>
+        <v>0.1800032215770744</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5117430633338531</v>
+        <v>0.5027651148543117</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1443575160087636</v>
+        <v>0.1664129614047292</v>
       </c>
       <c r="C59">
-        <v>-1765.513225069572</v>
+        <v>-2070.700770318379</v>
       </c>
       <c r="D59">
-        <v>1409.786774930428</v>
+        <v>1160.799229681622</v>
       </c>
       <c r="E59">
-        <v>2145</v>
+        <v>2201.2</v>
       </c>
       <c r="F59">
-        <v>3203.400000000001</v>
+        <v>3259.6</v>
       </c>
       <c r="G59">
         <v>28.1</v>
@@ -6125,45 +6125,45 @@
         <v>323.4</v>
       </c>
       <c r="M59">
-        <v>643.2427200000001</v>
+        <v>768.6136800000002</v>
       </c>
       <c r="N59">
-        <v>-319.8427200000001</v>
+        <v>-445.2136800000002</v>
       </c>
       <c r="O59">
-        <v>-65.88760032000003</v>
+        <v>-91.71401808000005</v>
       </c>
       <c r="P59">
-        <v>-253.9551196800001</v>
+        <v>-353.4996619200001</v>
       </c>
       <c r="Q59">
-        <v>-130.35511968</v>
+        <v>-229.8996619200001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09710623188332834</v>
+        <v>0.09881696453761152</v>
       </c>
       <c r="T59">
-        <v>1.184901429176174</v>
+        <v>1.224410266457541</v>
       </c>
       <c r="U59">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1035696136599882</v>
+        <v>0.08667605291646642</v>
       </c>
       <c r="W59">
-        <v>0.1800032215770744</v>
+        <v>0.2153617867222972</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.5027651148543117</v>
+        <v>0.4207575384294486</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1664129614047292</v>
+        <v>0.1683129614047292</v>
       </c>
       <c r="C60">
-        <v>-2070.700770318378</v>
+        <v>-2144.297242820385</v>
       </c>
       <c r="D60">
-        <v>1160.799229681622</v>
+        <v>1143.402757179615</v>
       </c>
       <c r="E60">
-        <v>2201.2</v>
+        <v>2257.4</v>
       </c>
       <c r="F60">
-        <v>3259.6</v>
+        <v>3315.8</v>
       </c>
       <c r="G60">
         <v>28.1</v>
@@ -6207,37 +6207,37 @@
         <v>323.4</v>
       </c>
       <c r="M60">
-        <v>768.61368</v>
+        <v>781.86564</v>
       </c>
       <c r="N60">
-        <v>-445.2136800000001</v>
+        <v>-458.46564</v>
       </c>
       <c r="O60">
-        <v>-91.71401808000002</v>
+        <v>-94.44392184000002</v>
       </c>
       <c r="P60">
-        <v>-353.4996619200001</v>
+        <v>-364.02171816</v>
       </c>
       <c r="Q60">
-        <v>-229.89966192</v>
+        <v>-240.42171816</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09881696453761152</v>
+        <v>0.1001100612336508</v>
       </c>
       <c r="T60">
-        <v>1.22441026645754</v>
+        <v>1.25427393149309</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.08667605291646643</v>
+        <v>0.08520696727381447</v>
       </c>
       <c r="W60">
-        <v>0.2153617867222972</v>
+        <v>0.2157081971168346</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4207575384294486</v>
+        <v>0.4136260547272547</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1683129614047292</v>
+        <v>0.1702129614047292</v>
       </c>
       <c r="C61">
-        <v>-2144.297242820385</v>
+        <v>-2217.379985294432</v>
       </c>
       <c r="D61">
-        <v>1143.402757179615</v>
+        <v>1126.520014705568</v>
       </c>
       <c r="E61">
-        <v>2257.4</v>
+        <v>2313.6</v>
       </c>
       <c r="F61">
-        <v>3315.8</v>
+        <v>3372</v>
       </c>
       <c r="G61">
         <v>28.1</v>
@@ -6289,37 +6289,37 @@
         <v>323.4</v>
       </c>
       <c r="M61">
-        <v>781.86564</v>
+        <v>795.1176</v>
       </c>
       <c r="N61">
-        <v>-458.46564</v>
+        <v>-471.7176000000001</v>
       </c>
       <c r="O61">
-        <v>-94.44392184000002</v>
+        <v>-97.17382560000001</v>
       </c>
       <c r="P61">
-        <v>-364.02171816</v>
+        <v>-374.5437744000001</v>
       </c>
       <c r="Q61">
-        <v>-240.42171816</v>
+        <v>-250.9437744000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1001100612336508</v>
+        <v>0.1014678127644921</v>
       </c>
       <c r="T61">
-        <v>1.25427393149309</v>
+        <v>1.285630779780417</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.08520696727381447</v>
+        <v>0.08378685115258422</v>
       </c>
       <c r="W61">
-        <v>0.2157081971168346</v>
+        <v>0.2160430604982206</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4136260547272547</v>
+        <v>0.4067322871484671</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1702129614047292</v>
+        <v>0.1721129614047292</v>
       </c>
       <c r="C62">
-        <v>-2217.379985294432</v>
+        <v>-2289.971422837873</v>
       </c>
       <c r="D62">
-        <v>1126.520014705568</v>
+        <v>1110.128577162127</v>
       </c>
       <c r="E62">
-        <v>2313.6</v>
+        <v>2369.8</v>
       </c>
       <c r="F62">
-        <v>3372</v>
+        <v>3428.2</v>
       </c>
       <c r="G62">
         <v>28.1</v>
@@ -6371,37 +6371,37 @@
         <v>323.4</v>
       </c>
       <c r="M62">
-        <v>795.1176</v>
+        <v>808.36956</v>
       </c>
       <c r="N62">
-        <v>-471.7176000000001</v>
+        <v>-484.96956</v>
       </c>
       <c r="O62">
-        <v>-97.17382560000001</v>
+        <v>-99.90372936000001</v>
       </c>
       <c r="P62">
-        <v>-374.5437744000001</v>
+        <v>-385.06583064</v>
       </c>
       <c r="Q62">
-        <v>-250.9437744000001</v>
+        <v>-261.46583064</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1014678127644921</v>
+        <v>0.1028951925789662</v>
       </c>
       <c r="T62">
-        <v>1.285630779780417</v>
+        <v>1.318595671569659</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.08378685115258422</v>
+        <v>0.08241329621565661</v>
       </c>
       <c r="W62">
-        <v>0.2160430604982206</v>
+        <v>0.2163669447523482</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4067322871484671</v>
+        <v>0.4000645447361971</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1721129614047292</v>
+        <v>0.1740129614047292</v>
       </c>
       <c r="C63">
-        <v>-2289.971422837873</v>
+        <v>-2362.092694080658</v>
       </c>
       <c r="D63">
-        <v>1110.128577162127</v>
+        <v>1094.207305919342</v>
       </c>
       <c r="E63">
-        <v>2369.8</v>
+        <v>2426</v>
       </c>
       <c r="F63">
-        <v>3428.2</v>
+        <v>3484.4</v>
       </c>
       <c r="G63">
         <v>28.1</v>
@@ -6453,37 +6453,37 @@
         <v>323.4</v>
       </c>
       <c r="M63">
-        <v>808.36956</v>
+        <v>821.62152</v>
       </c>
       <c r="N63">
-        <v>-484.96956</v>
+        <v>-498.2215200000001</v>
       </c>
       <c r="O63">
-        <v>-99.90372936000001</v>
+        <v>-102.63363312</v>
       </c>
       <c r="P63">
-        <v>-385.06583064</v>
+        <v>-395.58788688</v>
       </c>
       <c r="Q63">
-        <v>-261.46583064</v>
+        <v>-271.98788688</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1028951925789662</v>
+        <v>0.1043976976468338</v>
       </c>
       <c r="T63">
-        <v>1.318595671569659</v>
+        <v>1.353295557663597</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.08241329621565661</v>
+        <v>0.08108404950250085</v>
       </c>
       <c r="W63">
-        <v>0.2163669447523482</v>
+        <v>0.2166803811273103</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4000645447361971</v>
+        <v>0.3936118907888391</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1740129614047292</v>
+        <v>0.1759129614047292</v>
       </c>
       <c r="C64">
-        <v>-2362.092694080658</v>
+        <v>-2433.763742132444</v>
       </c>
       <c r="D64">
-        <v>1094.207305919342</v>
+        <v>1078.736257867556</v>
       </c>
       <c r="E64">
-        <v>2426</v>
+        <v>2482.2</v>
       </c>
       <c r="F64">
-        <v>3484.4</v>
+        <v>3540.6</v>
       </c>
       <c r="G64">
         <v>28.1</v>
@@ -6535,37 +6535,37 @@
         <v>323.4</v>
       </c>
       <c r="M64">
-        <v>821.62152</v>
+        <v>834.87348</v>
       </c>
       <c r="N64">
-        <v>-498.2215200000001</v>
+        <v>-511.47348</v>
       </c>
       <c r="O64">
-        <v>-102.63363312</v>
+        <v>-105.36353688</v>
       </c>
       <c r="P64">
-        <v>-395.58788688</v>
+        <v>-406.10994312</v>
       </c>
       <c r="Q64">
-        <v>-271.98788688</v>
+        <v>-282.5099431199999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1043976976468338</v>
+        <v>0.1059814192048563</v>
       </c>
       <c r="T64">
-        <v>1.353295557663597</v>
+        <v>1.389871113276127</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.08108404950250085</v>
+        <v>0.07979700109769926</v>
       </c>
       <c r="W64">
-        <v>0.2166803811273103</v>
+        <v>0.2169838671411625</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3936118907888391</v>
+        <v>0.3873640829985401</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1759129614047292</v>
+        <v>0.1778129614047292</v>
       </c>
       <c r="C65">
-        <v>-2433.763742132444</v>
+        <v>-2505.003397921844</v>
       </c>
       <c r="D65">
-        <v>1078.736257867556</v>
+        <v>1063.696602078157</v>
       </c>
       <c r="E65">
-        <v>2482.2</v>
+        <v>2538.4</v>
       </c>
       <c r="F65">
-        <v>3540.6</v>
+        <v>3596.8</v>
       </c>
       <c r="G65">
         <v>28.1</v>
@@ -6617,37 +6617,37 @@
         <v>323.4</v>
       </c>
       <c r="M65">
-        <v>834.87348</v>
+        <v>848.12544</v>
       </c>
       <c r="N65">
-        <v>-511.47348</v>
+        <v>-524.72544</v>
       </c>
       <c r="O65">
-        <v>-105.36353688</v>
+        <v>-108.09344064</v>
       </c>
       <c r="P65">
-        <v>-406.10994312</v>
+        <v>-416.63199936</v>
       </c>
       <c r="Q65">
-        <v>-282.5099431199999</v>
+        <v>-293.03199936</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1059814192048563</v>
+        <v>0.1076531252938801</v>
       </c>
       <c r="T65">
-        <v>1.389871113276127</v>
+        <v>1.428478644200464</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.07979700109769926</v>
+        <v>0.07855017295554771</v>
       </c>
       <c r="W65">
-        <v>0.2169838671411625</v>
+        <v>0.2172778692170819</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3873640829985401</v>
+        <v>0.3813115192016878</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1778129614047292</v>
+        <v>0.1797129614047292</v>
       </c>
       <c r="C66">
-        <v>-2505.003397921844</v>
+        <v>-2575.829456660074</v>
       </c>
       <c r="D66">
-        <v>1063.696602078157</v>
+        <v>1049.070543339926</v>
       </c>
       <c r="E66">
-        <v>2538.4</v>
+        <v>2594.6</v>
       </c>
       <c r="F66">
-        <v>3596.8</v>
+        <v>3653</v>
       </c>
       <c r="G66">
         <v>28.1</v>
@@ -6699,37 +6699,37 @@
         <v>323.4</v>
       </c>
       <c r="M66">
-        <v>848.12544</v>
+        <v>861.3774000000001</v>
       </c>
       <c r="N66">
-        <v>-524.72544</v>
+        <v>-537.9774000000001</v>
       </c>
       <c r="O66">
-        <v>-108.09344064</v>
+        <v>-110.8233444</v>
       </c>
       <c r="P66">
-        <v>-416.63199936</v>
+        <v>-427.1540556000001</v>
       </c>
       <c r="Q66">
-        <v>-293.03199936</v>
+        <v>-303.5540556000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1076531252938801</v>
+        <v>0.1094203574451338</v>
       </c>
       <c r="T66">
-        <v>1.428478644200464</v>
+        <v>1.469292319749049</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07855017295554771</v>
+        <v>0.07734170875623157</v>
       </c>
       <c r="W66">
-        <v>0.2172778692170819</v>
+        <v>0.2175628250752806</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3813115192016878</v>
+        <v>0.3754451881370465</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1797129614047292</v>
+        <v>0.1816129614047292</v>
       </c>
       <c r="C67">
-        <v>-2575.829456660074</v>
+        <v>-2646.258748081829</v>
       </c>
       <c r="D67">
-        <v>1049.070543339926</v>
+        <v>1034.841251918171</v>
       </c>
       <c r="E67">
-        <v>2594.6</v>
+        <v>2650.8</v>
       </c>
       <c r="F67">
-        <v>3653</v>
+        <v>3709.2</v>
       </c>
       <c r="G67">
         <v>28.1</v>
@@ -6781,37 +6781,37 @@
         <v>323.4</v>
       </c>
       <c r="M67">
-        <v>861.3774000000001</v>
+        <v>874.6293600000001</v>
       </c>
       <c r="N67">
-        <v>-537.9774000000001</v>
+        <v>-551.2293600000002</v>
       </c>
       <c r="O67">
-        <v>-110.8233444</v>
+        <v>-113.55324816</v>
       </c>
       <c r="P67">
-        <v>-427.1540556000001</v>
+        <v>-437.6761118400001</v>
       </c>
       <c r="Q67">
-        <v>-303.5540556000001</v>
+        <v>-314.0761118400001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1094203574451338</v>
+        <v>0.1112915444288142</v>
       </c>
       <c r="T67">
-        <v>1.469292319749049</v>
+        <v>1.512506799741668</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07734170875623157</v>
+        <v>0.07616986468416746</v>
       </c>
       <c r="W67">
-        <v>0.2175628250752806</v>
+        <v>0.2178391459074733</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3754451881370465</v>
+        <v>0.3697566246804246</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1816129614047292</v>
+        <v>0.1835129614047292</v>
       </c>
       <c r="C68">
-        <v>-2646.258748081829</v>
+        <v>-2716.307201046271</v>
       </c>
       <c r="D68">
-        <v>1034.841251918171</v>
+        <v>1020.992798953729</v>
       </c>
       <c r="E68">
-        <v>2650.8</v>
+        <v>2707</v>
       </c>
       <c r="F68">
-        <v>3709.2</v>
+        <v>3765.4</v>
       </c>
       <c r="G68">
         <v>28.1</v>
@@ -6863,37 +6863,37 @@
         <v>323.4</v>
       </c>
       <c r="M68">
-        <v>874.6293600000001</v>
+        <v>887.8813200000001</v>
       </c>
       <c r="N68">
-        <v>-551.2293600000002</v>
+        <v>-564.4813200000001</v>
       </c>
       <c r="O68">
-        <v>-113.55324816</v>
+        <v>-116.28315192</v>
       </c>
       <c r="P68">
-        <v>-437.6761118400001</v>
+        <v>-448.1981680800001</v>
       </c>
       <c r="Q68">
-        <v>-314.0761118400001</v>
+        <v>-324.5981680800001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1112915444288142</v>
+        <v>0.1132761366842328</v>
       </c>
       <c r="T68">
-        <v>1.512506799741668</v>
+        <v>1.558340339127779</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.07616986468416746</v>
+        <v>0.07503300103216497</v>
       </c>
       <c r="W68">
-        <v>0.2178391459074733</v>
+        <v>0.2181072183566155</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3697566246804246</v>
+        <v>0.3642378690881795</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1835129614047292</v>
+        <v>0.1854129614047292</v>
       </c>
       <c r="C69">
-        <v>-2716.307201046271</v>
+        <v>-2785.989903019519</v>
       </c>
       <c r="D69">
-        <v>1020.992798953729</v>
+        <v>1007.510096980481</v>
       </c>
       <c r="E69">
-        <v>2707</v>
+        <v>2763.2</v>
       </c>
       <c r="F69">
-        <v>3765.4</v>
+        <v>3821.6</v>
       </c>
       <c r="G69">
         <v>28.1</v>
@@ -6945,37 +6945,37 @@
         <v>323.4</v>
       </c>
       <c r="M69">
-        <v>887.8813200000001</v>
+        <v>901.1332800000001</v>
       </c>
       <c r="N69">
-        <v>-564.4813200000001</v>
+        <v>-577.7332800000001</v>
       </c>
       <c r="O69">
-        <v>-116.28315192</v>
+        <v>-119.01305568</v>
       </c>
       <c r="P69">
-        <v>-448.1981680800001</v>
+        <v>-458.7202243200001</v>
       </c>
       <c r="Q69">
-        <v>-324.5981680800001</v>
+        <v>-335.1202243200001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1132761366842328</v>
+        <v>0.1153847659556151</v>
       </c>
       <c r="T69">
-        <v>1.558340339127779</v>
+        <v>1.607038474725522</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07503300103216497</v>
+        <v>0.07392957454639783</v>
       </c>
       <c r="W69">
-        <v>0.2181072183566155</v>
+        <v>0.2183674063219594</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3642378690881795</v>
+        <v>0.3588814298368826</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1854129614047292</v>
+        <v>0.1873129614047293</v>
       </c>
       <c r="C70">
-        <v>-2785.989903019519</v>
+        <v>-2855.321154905575</v>
       </c>
       <c r="D70">
-        <v>1007.510096980481</v>
+        <v>994.3788450944253</v>
       </c>
       <c r="E70">
-        <v>2763.2</v>
+        <v>2819.4</v>
       </c>
       <c r="F70">
-        <v>3821.6</v>
+        <v>3877.8</v>
       </c>
       <c r="G70">
         <v>28.1</v>
@@ -7027,37 +7027,37 @@
         <v>323.4</v>
       </c>
       <c r="M70">
-        <v>901.1332800000001</v>
+        <v>914.3852400000001</v>
       </c>
       <c r="N70">
-        <v>-577.7332800000001</v>
+        <v>-590.9852400000001</v>
       </c>
       <c r="O70">
-        <v>-119.01305568</v>
+        <v>-121.74295944</v>
       </c>
       <c r="P70">
-        <v>-458.7202243200001</v>
+        <v>-469.24228056</v>
       </c>
       <c r="Q70">
-        <v>-335.1202243200001</v>
+        <v>-345.64228056</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1153847659556151</v>
+        <v>0.1176294358251511</v>
       </c>
       <c r="T70">
-        <v>1.607038474725522</v>
+        <v>1.658878425523119</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07392957454639783</v>
+        <v>0.07285813143702975</v>
       </c>
       <c r="W70">
-        <v>0.2183674063219594</v>
+        <v>0.2186200526071484</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3588814298368826</v>
+        <v>0.3536802496943192</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1873129614047293</v>
+        <v>0.1892129614047293</v>
       </c>
       <c r="C71">
-        <v>-2855.321154905575</v>
+        <v>-2924.314521644636</v>
       </c>
       <c r="D71">
-        <v>994.3788450944253</v>
+        <v>981.5854783553639</v>
       </c>
       <c r="E71">
-        <v>2819.4</v>
+        <v>2875.6</v>
       </c>
       <c r="F71">
-        <v>3877.8</v>
+        <v>3934</v>
       </c>
       <c r="G71">
         <v>28.1</v>
@@ -7109,37 +7109,37 @@
         <v>323.4</v>
       </c>
       <c r="M71">
-        <v>914.3852400000001</v>
+        <v>927.6372000000001</v>
       </c>
       <c r="N71">
-        <v>-590.9852400000001</v>
+        <v>-604.2372000000001</v>
       </c>
       <c r="O71">
-        <v>-121.74295944</v>
+        <v>-124.4728632</v>
       </c>
       <c r="P71">
-        <v>-469.24228056</v>
+        <v>-479.7643368000001</v>
       </c>
       <c r="Q71">
-        <v>-345.64228056</v>
+        <v>-356.1643368000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1176294358251511</v>
+        <v>0.1200237503526561</v>
       </c>
       <c r="T71">
-        <v>1.658878425523119</v>
+        <v>1.714174373040557</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07285813143702975</v>
+        <v>0.07181730098792932</v>
       </c>
       <c r="W71">
-        <v>0.2186200526071484</v>
+        <v>0.2188654804270463</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3536802496943192</v>
+        <v>0.3486276746986861</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1892129614047293</v>
+        <v>0.1911129614047292</v>
       </c>
       <c r="C72">
-        <v>-2924.314521644636</v>
+        <v>-2992.982878955127</v>
       </c>
       <c r="D72">
-        <v>981.5854783553639</v>
+        <v>969.1171210448734</v>
       </c>
       <c r="E72">
-        <v>2875.6</v>
+        <v>2931.8</v>
       </c>
       <c r="F72">
-        <v>3934</v>
+        <v>3990.2</v>
       </c>
       <c r="G72">
         <v>28.1</v>
@@ -7191,37 +7191,37 @@
         <v>323.4</v>
       </c>
       <c r="M72">
-        <v>927.6372000000001</v>
+        <v>940.8891600000001</v>
       </c>
       <c r="N72">
-        <v>-604.2372000000001</v>
+        <v>-617.4891600000001</v>
       </c>
       <c r="O72">
-        <v>-124.4728632</v>
+        <v>-127.20276696</v>
       </c>
       <c r="P72">
-        <v>-479.7643368000001</v>
+        <v>-490.2863930400001</v>
       </c>
       <c r="Q72">
-        <v>-356.1643368000001</v>
+        <v>-366.68639304</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1200237503526561</v>
+        <v>0.1225831900199891</v>
       </c>
       <c r="T72">
-        <v>1.714174373040557</v>
+        <v>1.773283834179887</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07181730098792932</v>
+        <v>0.0708057897064092</v>
       </c>
       <c r="W72">
-        <v>0.2188654804270463</v>
+        <v>0.2191039947872287</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3486276746986861</v>
+        <v>0.3437174257592679</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1911129614047292</v>
+        <v>0.1930129614047292</v>
       </c>
       <c r="C73">
-        <v>-2992.982878955127</v>
+        <v>-3061.338456558031</v>
       </c>
       <c r="D73">
-        <v>969.1171210448734</v>
+        <v>956.9615434419686</v>
       </c>
       <c r="E73">
-        <v>2931.8</v>
+        <v>2988</v>
       </c>
       <c r="F73">
-        <v>3990.2</v>
+        <v>4046.4</v>
       </c>
       <c r="G73">
         <v>28.1</v>
@@ -7273,37 +7273,37 @@
         <v>323.4</v>
       </c>
       <c r="M73">
-        <v>940.8891599999999</v>
+        <v>954.14112</v>
       </c>
       <c r="N73">
-        <v>-617.48916</v>
+        <v>-630.74112</v>
       </c>
       <c r="O73">
-        <v>-127.20276696</v>
+        <v>-129.93267072</v>
       </c>
       <c r="P73">
-        <v>-490.28639304</v>
+        <v>-500.80844928</v>
       </c>
       <c r="Q73">
-        <v>-366.6863930399999</v>
+        <v>-377.20844928</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1225831900199891</v>
+        <v>0.1253254468064172</v>
       </c>
       <c r="T73">
-        <v>1.773283834179886</v>
+        <v>1.836615399686311</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.0708057897064092</v>
+        <v>0.06982237596048685</v>
       </c>
       <c r="W73">
-        <v>0.2191039947872287</v>
+        <v>0.2193358837485172</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.343717425759268</v>
+        <v>0.3389435726237225</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1930129614047292</v>
+        <v>0.1949129614047292</v>
       </c>
       <c r="C74">
-        <v>-3061.338456558031</v>
+        <v>-3129.392878188567</v>
       </c>
       <c r="D74">
-        <v>956.9615434419686</v>
+        <v>945.1071218114325</v>
       </c>
       <c r="E74">
-        <v>2988</v>
+        <v>3044.199999999999</v>
       </c>
       <c r="F74">
-        <v>4046.4</v>
+        <v>4102.599999999999</v>
       </c>
       <c r="G74">
         <v>28.1</v>
@@ -7355,37 +7355,37 @@
         <v>323.4</v>
       </c>
       <c r="M74">
-        <v>954.14112</v>
+        <v>967.3930799999999</v>
       </c>
       <c r="N74">
-        <v>-630.74112</v>
+        <v>-643.99308</v>
       </c>
       <c r="O74">
-        <v>-129.93267072</v>
+        <v>-132.66257448</v>
       </c>
       <c r="P74">
-        <v>-500.80844928</v>
+        <v>-511.33050552</v>
       </c>
       <c r="Q74">
-        <v>-377.20844928</v>
+        <v>-387.73050552</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1253254468064172</v>
+        <v>0.1282708337251734</v>
       </c>
       <c r="T74">
-        <v>1.836615399686311</v>
+        <v>1.904638192267285</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06982237596048685</v>
+        <v>0.06886590505691854</v>
       </c>
       <c r="W74">
-        <v>0.2193358837485172</v>
+        <v>0.2195614195875786</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3389435726237225</v>
+        <v>0.3343005099850415</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1949129614047292</v>
+        <v>0.1968129614047292</v>
       </c>
       <c r="C75">
-        <v>-3129.392878188567</v>
+        <v>-3197.157198670359</v>
       </c>
       <c r="D75">
-        <v>945.1071218114325</v>
+        <v>933.5428013296408</v>
       </c>
       <c r="E75">
-        <v>3044.199999999999</v>
+        <v>3100.4</v>
       </c>
       <c r="F75">
-        <v>4102.599999999999</v>
+        <v>4158.8</v>
       </c>
       <c r="G75">
         <v>28.1</v>
@@ -7437,37 +7437,37 @@
         <v>323.4</v>
       </c>
       <c r="M75">
-        <v>967.3930799999999</v>
+        <v>980.6450400000001</v>
       </c>
       <c r="N75">
-        <v>-643.99308</v>
+        <v>-657.2450400000001</v>
       </c>
       <c r="O75">
-        <v>-132.66257448</v>
+        <v>-135.39247824</v>
       </c>
       <c r="P75">
-        <v>-511.33050552</v>
+        <v>-521.8525617600001</v>
       </c>
       <c r="Q75">
-        <v>-387.73050552</v>
+        <v>-398.25256176</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1282708337251734</v>
+        <v>0.1314427888684493</v>
       </c>
       <c r="T75">
-        <v>1.904638192267285</v>
+        <v>1.977893507354488</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06886590505691854</v>
+        <v>0.06793528471831152</v>
       </c>
       <c r="W75">
-        <v>0.2195614195875786</v>
+        <v>0.2197808598634221</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3343005099850415</v>
+        <v>0.3297829355257841</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1968129614047292</v>
+        <v>0.1987129614047292</v>
       </c>
       <c r="C76">
-        <v>-3197.157198670359</v>
+        <v>-3264.641938300683</v>
       </c>
       <c r="D76">
-        <v>933.5428013296408</v>
+        <v>922.2580616993165</v>
       </c>
       <c r="E76">
-        <v>3100.4</v>
+        <v>3156.6</v>
       </c>
       <c r="F76">
-        <v>4158.8</v>
+        <v>4215</v>
       </c>
       <c r="G76">
         <v>28.1</v>
@@ -7519,37 +7519,37 @@
         <v>323.4</v>
       </c>
       <c r="M76">
-        <v>980.6450400000001</v>
+        <v>993.897</v>
       </c>
       <c r="N76">
-        <v>-657.2450400000001</v>
+        <v>-670.4970000000001</v>
       </c>
       <c r="O76">
-        <v>-135.39247824</v>
+        <v>-138.122382</v>
       </c>
       <c r="P76">
-        <v>-521.8525617600001</v>
+        <v>-532.3746180000001</v>
       </c>
       <c r="Q76">
-        <v>-398.25256176</v>
+        <v>-408.774618</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1314427888684493</v>
+        <v>0.1348685004231873</v>
       </c>
       <c r="T76">
-        <v>1.977893507354488</v>
+        <v>2.057009247648668</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06793528471831152</v>
+        <v>0.06702948092206737</v>
       </c>
       <c r="W76">
-        <v>0.2197808598634221</v>
+        <v>0.2199944483985765</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3297829355257841</v>
+        <v>0.3253858297187736</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1987129614047292</v>
+        <v>0.2006129614047292</v>
       </c>
       <c r="C77">
-        <v>-3264.641938300683</v>
+        <v>-3331.857114771587</v>
       </c>
       <c r="D77">
-        <v>922.2580616993165</v>
+        <v>911.2428852284125</v>
       </c>
       <c r="E77">
-        <v>3156.6</v>
+        <v>3212.8</v>
       </c>
       <c r="F77">
-        <v>4215</v>
+        <v>4271.2</v>
       </c>
       <c r="G77">
         <v>28.1</v>
@@ -7601,37 +7601,37 @@
         <v>323.4</v>
       </c>
       <c r="M77">
-        <v>993.897</v>
+        <v>1007.14896</v>
       </c>
       <c r="N77">
-        <v>-670.4970000000001</v>
+        <v>-683.74896</v>
       </c>
       <c r="O77">
-        <v>-138.122382</v>
+        <v>-140.85228576</v>
       </c>
       <c r="P77">
-        <v>-532.3746180000001</v>
+        <v>-542.89667424</v>
       </c>
       <c r="Q77">
-        <v>-408.774618</v>
+        <v>-419.29667424</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1348685004231873</v>
+        <v>0.1385796879408201</v>
       </c>
       <c r="T77">
-        <v>2.057009247648668</v>
+        <v>2.142717966300696</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06702948092206737</v>
+        <v>0.06614751406782965</v>
       </c>
       <c r="W77">
-        <v>0.2199944483985765</v>
+        <v>0.2202024161828058</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3253858297187736</v>
+        <v>0.3211044372224739</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2006129614047292</v>
+        <v>0.2025129614047292</v>
       </c>
       <c r="C78">
-        <v>-3331.857114771587</v>
+        <v>-3398.812272830472</v>
       </c>
       <c r="D78">
-        <v>911.2428852284125</v>
+        <v>900.4877271695291</v>
       </c>
       <c r="E78">
-        <v>3212.8</v>
+        <v>3269</v>
       </c>
       <c r="F78">
-        <v>4271.2</v>
+        <v>4327.400000000001</v>
       </c>
       <c r="G78">
         <v>28.1</v>
@@ -7683,37 +7683,37 @@
         <v>323.4</v>
       </c>
       <c r="M78">
-        <v>1007.14896</v>
+        <v>1020.40092</v>
       </c>
       <c r="N78">
-        <v>-683.74896</v>
+        <v>-697.0009200000002</v>
       </c>
       <c r="O78">
-        <v>-140.85228576</v>
+        <v>-143.58218952</v>
       </c>
       <c r="P78">
-        <v>-542.89667424</v>
+        <v>-553.4187304800001</v>
       </c>
       <c r="Q78">
-        <v>-419.29667424</v>
+        <v>-429.8187304800001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1385796879408201</v>
+        <v>0.142613587416508</v>
       </c>
       <c r="T78">
-        <v>2.142717966300696</v>
+        <v>2.235879617009422</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06614751406782965</v>
+        <v>0.06528845544357212</v>
       </c>
       <c r="W78">
-        <v>0.2202024161828058</v>
+        <v>0.2204049822064057</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3211044372224739</v>
+        <v>0.3169342497260782</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2025129614047292</v>
+        <v>0.2044129614047292</v>
       </c>
       <c r="C79">
-        <v>-3398.812272830472</v>
+        <v>-3465.516511864713</v>
       </c>
       <c r="D79">
-        <v>900.4877271695291</v>
+        <v>889.9834881352873</v>
       </c>
       <c r="E79">
-        <v>3269</v>
+        <v>3325.2</v>
       </c>
       <c r="F79">
-        <v>4327.400000000001</v>
+        <v>4383.6</v>
       </c>
       <c r="G79">
         <v>28.1</v>
@@ -7765,37 +7765,37 @@
         <v>323.4</v>
       </c>
       <c r="M79">
-        <v>1020.40092</v>
+        <v>1033.65288</v>
       </c>
       <c r="N79">
-        <v>-697.0009200000002</v>
+        <v>-710.2528800000001</v>
       </c>
       <c r="O79">
-        <v>-143.58218952</v>
+        <v>-146.31209328</v>
       </c>
       <c r="P79">
-        <v>-553.4187304800001</v>
+        <v>-563.9407867200001</v>
       </c>
       <c r="Q79">
-        <v>-429.8187304800001</v>
+        <v>-440.3407867200001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.142613587416508</v>
+        <v>0.1470142050263492</v>
       </c>
       <c r="T79">
-        <v>2.235879617009422</v>
+        <v>2.337510508691668</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06528845544357212</v>
+        <v>0.06445142396352631</v>
       </c>
       <c r="W79">
-        <v>0.2204049822064057</v>
+        <v>0.2206023542294005</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3169342497260782</v>
+        <v>0.3128709901142054</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2044129614047292</v>
+        <v>0.2063129614047292</v>
       </c>
       <c r="C80">
-        <v>-3465.516511864713</v>
+        <v>-3531.978511577903</v>
       </c>
       <c r="D80">
-        <v>889.9834881352873</v>
+        <v>879.7214884220975</v>
       </c>
       <c r="E80">
-        <v>3325.2</v>
+        <v>3381.4</v>
       </c>
       <c r="F80">
-        <v>4383.6</v>
+        <v>4439.8</v>
       </c>
       <c r="G80">
         <v>28.1</v>
@@ -7847,37 +7847,37 @@
         <v>323.4</v>
       </c>
       <c r="M80">
-        <v>1033.65288</v>
+        <v>1046.90484</v>
       </c>
       <c r="N80">
-        <v>-710.2528800000001</v>
+        <v>-723.5048400000002</v>
       </c>
       <c r="O80">
-        <v>-146.31209328</v>
+        <v>-149.04199704</v>
       </c>
       <c r="P80">
-        <v>-563.9407867200001</v>
+        <v>-574.4628429600001</v>
       </c>
       <c r="Q80">
-        <v>-440.3407867200001</v>
+        <v>-450.8628429600001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1470142050263492</v>
+        <v>0.151833929075223</v>
       </c>
       <c r="T80">
-        <v>2.337510508691668</v>
+        <v>2.448820532915081</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06445142396352631</v>
+        <v>0.06363558315386143</v>
       </c>
       <c r="W80">
-        <v>0.2206023542294005</v>
+        <v>0.2207947294923195</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3128709901142054</v>
+        <v>0.3089105978342788</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2063129614047292</v>
+        <v>0.2082129614047292</v>
       </c>
       <c r="C81">
-        <v>-3531.978511577903</v>
+        <v>-3598.206555909955</v>
       </c>
       <c r="D81">
-        <v>879.7214884220975</v>
+        <v>869.6934440900452</v>
       </c>
       <c r="E81">
-        <v>3381.4</v>
+        <v>3437.6</v>
       </c>
       <c r="F81">
-        <v>4439.8</v>
+        <v>4496</v>
       </c>
       <c r="G81">
         <v>28.1</v>
@@ -7929,37 +7929,37 @@
         <v>323.4</v>
       </c>
       <c r="M81">
-        <v>1046.90484</v>
+        <v>1060.1568</v>
       </c>
       <c r="N81">
-        <v>-723.5048400000002</v>
+        <v>-736.7568</v>
       </c>
       <c r="O81">
-        <v>-149.04199704</v>
+        <v>-151.7719008</v>
       </c>
       <c r="P81">
-        <v>-574.4628429600001</v>
+        <v>-584.9848992</v>
       </c>
       <c r="Q81">
-        <v>-450.8628429600001</v>
+        <v>-461.3848991999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.151833929075223</v>
+        <v>0.1571356255289842</v>
       </c>
       <c r="T81">
-        <v>2.448820532915081</v>
+        <v>2.571261559560835</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06363558315386143</v>
+        <v>0.06284013836443818</v>
       </c>
       <c r="W81">
-        <v>0.2207947294923195</v>
+        <v>0.2209822953736655</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3089105978342788</v>
+        <v>0.3050492153613503</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2082129614047292</v>
+        <v>0.2101129614047292</v>
       </c>
       <c r="C82">
-        <v>-3598.206555909955</v>
+        <v>-3664.208555339653</v>
       </c>
       <c r="D82">
-        <v>869.6934440900452</v>
+        <v>859.8914446603475</v>
       </c>
       <c r="E82">
-        <v>3437.6</v>
+        <v>3493.800000000001</v>
       </c>
       <c r="F82">
-        <v>4496</v>
+        <v>4552.200000000001</v>
       </c>
       <c r="G82">
         <v>28.1</v>
@@ -8011,37 +8011,37 @@
         <v>323.4</v>
       </c>
       <c r="M82">
-        <v>1060.1568</v>
+        <v>1073.40876</v>
       </c>
       <c r="N82">
-        <v>-736.7568</v>
+        <v>-750.0087600000003</v>
       </c>
       <c r="O82">
-        <v>-151.7719008</v>
+        <v>-154.5018045600001</v>
       </c>
       <c r="P82">
-        <v>-584.9848992</v>
+        <v>-595.5069554400002</v>
       </c>
       <c r="Q82">
-        <v>-461.3848991999999</v>
+        <v>-471.9069554400002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1571356255289842</v>
+        <v>0.1629953952936675</v>
       </c>
       <c r="T82">
-        <v>2.571261559560835</v>
+        <v>2.706591115327195</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06284013836443818</v>
+        <v>0.06206433418709941</v>
       </c>
       <c r="W82">
-        <v>0.2209822953736655</v>
+        <v>0.221165229998682</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3050492153613503</v>
+        <v>0.3012831756655311</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2101129614047292</v>
+        <v>0.2120129614047292</v>
       </c>
       <c r="C83">
-        <v>-3664.208555339653</v>
+        <v>-3729.992067695819</v>
       </c>
       <c r="D83">
-        <v>859.8914446603475</v>
+        <v>850.3079323041816</v>
       </c>
       <c r="E83">
-        <v>3493.800000000001</v>
+        <v>3550</v>
       </c>
       <c r="F83">
-        <v>4552.200000000001</v>
+        <v>4608.400000000001</v>
       </c>
       <c r="G83">
         <v>28.1</v>
@@ -8093,37 +8093,37 @@
         <v>323.4</v>
       </c>
       <c r="M83">
-        <v>1073.40876</v>
+        <v>1086.66072</v>
       </c>
       <c r="N83">
-        <v>-750.0087600000003</v>
+        <v>-763.2607200000001</v>
       </c>
       <c r="O83">
-        <v>-154.5018045600001</v>
+        <v>-157.23170832</v>
       </c>
       <c r="P83">
-        <v>-595.5069554400002</v>
+        <v>-606.0290116800001</v>
       </c>
       <c r="Q83">
-        <v>-471.9069554400002</v>
+        <v>-482.42901168</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1629953952936675</v>
+        <v>0.1695062505877602</v>
       </c>
       <c r="T83">
-        <v>2.706591115327195</v>
+        <v>2.856957288400928</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06206433418709941</v>
+        <v>0.0613074520628665</v>
       </c>
       <c r="W83">
-        <v>0.221165229998682</v>
+        <v>0.2213437028035761</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3012831756655311</v>
+        <v>0.2976089905964393</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2120129614047292</v>
+        <v>0.2139129614047292</v>
       </c>
       <c r="C84">
-        <v>-3729.992067695819</v>
+        <v>-3795.564317592175</v>
       </c>
       <c r="D84">
-        <v>850.3079323041816</v>
+        <v>840.9356824078247</v>
       </c>
       <c r="E84">
-        <v>3550</v>
+        <v>3606.2</v>
       </c>
       <c r="F84">
-        <v>4608.400000000001</v>
+        <v>4664.6</v>
       </c>
       <c r="G84">
         <v>28.1</v>
@@ -8175,37 +8175,37 @@
         <v>323.4</v>
       </c>
       <c r="M84">
-        <v>1086.66072</v>
+        <v>1099.91268</v>
       </c>
       <c r="N84">
-        <v>-763.2607200000001</v>
+        <v>-776.5126800000002</v>
       </c>
       <c r="O84">
-        <v>-157.23170832</v>
+        <v>-159.96161208</v>
       </c>
       <c r="P84">
-        <v>-606.0290116800001</v>
+        <v>-616.5510679200002</v>
       </c>
       <c r="Q84">
-        <v>-482.42901168</v>
+        <v>-492.9510679200001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1695062505877602</v>
+        <v>0.1767830888576285</v>
       </c>
       <c r="T84">
-        <v>2.856957288400928</v>
+        <v>3.025013599483336</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0613074520628665</v>
+        <v>0.06056880806210907</v>
       </c>
       <c r="W84">
-        <v>0.2213437028035761</v>
+        <v>0.2215178750589547</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2976089905964393</v>
+        <v>0.2940233401073256</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2139129614047292</v>
+        <v>0.2158129614047293</v>
       </c>
       <c r="C85">
-        <v>-3795.564317592175</v>
+        <v>-3860.932214590935</v>
       </c>
       <c r="D85">
-        <v>840.9356824078247</v>
+        <v>831.7677854090654</v>
       </c>
       <c r="E85">
-        <v>3606.2</v>
+        <v>3662.4</v>
       </c>
       <c r="F85">
-        <v>4664.6</v>
+        <v>4720.8</v>
       </c>
       <c r="G85">
         <v>28.1</v>
@@ -8257,37 +8257,37 @@
         <v>323.4</v>
       </c>
       <c r="M85">
-        <v>1099.91268</v>
+        <v>1113.16464</v>
       </c>
       <c r="N85">
-        <v>-776.5126800000002</v>
+        <v>-789.7646400000002</v>
       </c>
       <c r="O85">
-        <v>-159.96161208</v>
+        <v>-162.6915158400001</v>
       </c>
       <c r="P85">
-        <v>-616.5510679200002</v>
+        <v>-627.0731241600001</v>
       </c>
       <c r="Q85">
-        <v>-492.9510679200001</v>
+        <v>-503.4731241600001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1767830888576285</v>
+        <v>0.1849695319112303</v>
       </c>
       <c r="T85">
-        <v>3.025013599483336</v>
+        <v>3.214076949451045</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06056880806210907</v>
+        <v>0.05984775082327443</v>
       </c>
       <c r="W85">
-        <v>0.2215178750589547</v>
+        <v>0.2216879003558719</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2940233401073256</v>
+        <v>0.290523062248905</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2158129614047292</v>
+        <v>0.2177129614047292</v>
       </c>
       <c r="C86">
-        <v>-3860.932214590935</v>
+        <v>-3926.102370191079</v>
       </c>
       <c r="D86">
-        <v>831.7677854090654</v>
+        <v>822.7976298089212</v>
       </c>
       <c r="E86">
-        <v>3662.4</v>
+        <v>3718.6</v>
       </c>
       <c r="F86">
-        <v>4720.8</v>
+        <v>4777</v>
       </c>
       <c r="G86">
         <v>28.1</v>
@@ -8339,37 +8339,37 @@
         <v>323.4</v>
       </c>
       <c r="M86">
-        <v>1113.16464</v>
+        <v>1126.4166</v>
       </c>
       <c r="N86">
-        <v>-789.7646400000002</v>
+        <v>-803.0166</v>
       </c>
       <c r="O86">
-        <v>-162.6915158400001</v>
+        <v>-165.4214196</v>
       </c>
       <c r="P86">
-        <v>-627.0731241600001</v>
+        <v>-637.5951804</v>
       </c>
       <c r="Q86">
-        <v>-503.4731241600001</v>
+        <v>-513.9951804</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1849695319112302</v>
+        <v>0.1942475007053122</v>
       </c>
       <c r="T86">
-        <v>3.214076949451043</v>
+        <v>3.428348746081113</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05984775082327443</v>
+        <v>0.05914365963711827</v>
       </c>
       <c r="W86">
-        <v>0.2216879003558719</v>
+        <v>0.2218539250575675</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.290523062248905</v>
+        <v>0.2871051438695061</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2177129614047292</v>
+        <v>0.2196129614047292</v>
       </c>
       <c r="C87">
-        <v>-3926.102370191079</v>
+        <v>-3991.081113729114</v>
       </c>
       <c r="D87">
-        <v>822.7976298089212</v>
+        <v>814.0188862708854</v>
       </c>
       <c r="E87">
-        <v>3718.6</v>
+        <v>3774.8</v>
       </c>
       <c r="F87">
-        <v>4777</v>
+        <v>4833.2</v>
       </c>
       <c r="G87">
         <v>28.1</v>
@@ -8421,37 +8421,37 @@
         <v>323.4</v>
       </c>
       <c r="M87">
-        <v>1126.4166</v>
+        <v>1139.66856</v>
       </c>
       <c r="N87">
-        <v>-803.0166</v>
+        <v>-816.2685600000001</v>
       </c>
       <c r="O87">
-        <v>-165.4214196</v>
+        <v>-168.15132336</v>
       </c>
       <c r="P87">
-        <v>-637.5951804</v>
+        <v>-648.1172366400001</v>
       </c>
       <c r="Q87">
-        <v>-513.9951804</v>
+        <v>-524.5172366400001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1942475007053122</v>
+        <v>0.2048508936128345</v>
       </c>
       <c r="T87">
-        <v>3.428348746081113</v>
+        <v>3.673230799372621</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05914365963711827</v>
+        <v>0.05845594266459364</v>
       </c>
       <c r="W87">
-        <v>0.2218539250575675</v>
+        <v>0.2220160887196888</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2871051438695061</v>
+        <v>0.2837667119640468</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2196129614047292</v>
+        <v>0.2215129614047292</v>
       </c>
       <c r="C88">
-        <v>-3991.081113729114</v>
+        <v>-4055.874507272665</v>
       </c>
       <c r="D88">
-        <v>814.0188862708854</v>
+        <v>805.4254927273342</v>
       </c>
       <c r="E88">
-        <v>3774.8</v>
+        <v>3831</v>
       </c>
       <c r="F88">
-        <v>4833.2</v>
+        <v>4889.4</v>
       </c>
       <c r="G88">
         <v>28.1</v>
@@ -8503,37 +8503,37 @@
         <v>323.4</v>
       </c>
       <c r="M88">
-        <v>1139.66856</v>
+        <v>1152.92052</v>
       </c>
       <c r="N88">
-        <v>-816.2685600000001</v>
+        <v>-829.5205199999999</v>
       </c>
       <c r="O88">
-        <v>-168.15132336</v>
+        <v>-170.88122712</v>
       </c>
       <c r="P88">
-        <v>-648.1172366400001</v>
+        <v>-658.6392928799999</v>
       </c>
       <c r="Q88">
-        <v>-524.5172366400001</v>
+        <v>-535.0392928799998</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2048508936128345</v>
+        <v>0.2170855777368987</v>
       </c>
       <c r="T88">
-        <v>3.673230799372621</v>
+        <v>3.955787014708976</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05845594266459364</v>
+        <v>0.05778403527764429</v>
       </c>
       <c r="W88">
-        <v>0.2220160887196888</v>
+        <v>0.2221745244815315</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2837667119640468</v>
+        <v>0.2805050256196325</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2215129614047292</v>
+        <v>0.2234129614047292</v>
       </c>
       <c r="C89">
-        <v>-4055.874507272665</v>
+        <v>-4120.488359580555</v>
       </c>
       <c r="D89">
-        <v>805.4254927273342</v>
+        <v>797.0116404194451</v>
       </c>
       <c r="E89">
-        <v>3831</v>
+        <v>3887.2</v>
       </c>
       <c r="F89">
-        <v>4889.4</v>
+        <v>4945.6</v>
       </c>
       <c r="G89">
         <v>28.1</v>
@@ -8585,37 +8585,37 @@
         <v>323.4</v>
       </c>
       <c r="M89">
-        <v>1152.92052</v>
+        <v>1166.17248</v>
       </c>
       <c r="N89">
-        <v>-829.5205199999999</v>
+        <v>-842.7724800000002</v>
       </c>
       <c r="O89">
-        <v>-170.88122712</v>
+        <v>-173.61113088</v>
       </c>
       <c r="P89">
-        <v>-658.6392928799999</v>
+        <v>-669.1613491200002</v>
       </c>
       <c r="Q89">
-        <v>-535.0392928799998</v>
+        <v>-545.5613491200002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2170855777368987</v>
+        <v>0.2313593758816403</v>
       </c>
       <c r="T89">
-        <v>3.955787014708976</v>
+        <v>4.285435932601391</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05778403527764429</v>
+        <v>0.0571273985131256</v>
       </c>
       <c r="W89">
-        <v>0.2221745244815315</v>
+        <v>0.222329359430605</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2805050256196325</v>
+        <v>0.2773174685103185</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2234129614047292</v>
+        <v>0.2253129614047292</v>
       </c>
       <c r="C90">
-        <v>-4120.488359580555</v>
+        <v>-4184.928239196927</v>
       </c>
       <c r="D90">
-        <v>797.0116404194451</v>
+        <v>788.7717608030729</v>
       </c>
       <c r="E90">
-        <v>3887.2</v>
+        <v>3943.4</v>
       </c>
       <c r="F90">
-        <v>4945.6</v>
+        <v>5001.8</v>
       </c>
       <c r="G90">
         <v>28.1</v>
@@ -8667,37 +8667,37 @@
         <v>323.4</v>
       </c>
       <c r="M90">
-        <v>1166.17248</v>
+        <v>1179.42444</v>
       </c>
       <c r="N90">
-        <v>-842.7724800000002</v>
+        <v>-856.02444</v>
       </c>
       <c r="O90">
-        <v>-173.61113088</v>
+        <v>-176.34103464</v>
       </c>
       <c r="P90">
-        <v>-669.1613491200002</v>
+        <v>-679.6834053600001</v>
       </c>
       <c r="Q90">
-        <v>-545.5613491200002</v>
+        <v>-556.08340536</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2313593758816403</v>
+        <v>0.2482284100526985</v>
       </c>
       <c r="T90">
-        <v>4.285435932601391</v>
+        <v>4.675021017383336</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0571273985131256</v>
+        <v>0.05648551763095565</v>
       </c>
       <c r="W90">
-        <v>0.222329359430605</v>
+        <v>0.2224807149426207</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2773174685103185</v>
+        <v>0.274201541897843</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2253129614047292</v>
+        <v>0.2272129614047292</v>
       </c>
       <c r="C91">
-        <v>-4184.928239196927</v>
+        <v>-4249.199486741449</v>
       </c>
       <c r="D91">
-        <v>788.7717608030729</v>
+        <v>780.7005132585514</v>
       </c>
       <c r="E91">
-        <v>3943.4</v>
+        <v>3999.6</v>
       </c>
       <c r="F91">
-        <v>5001.8</v>
+        <v>5058</v>
       </c>
       <c r="G91">
         <v>28.1</v>
@@ -8749,37 +8749,37 @@
         <v>323.4</v>
       </c>
       <c r="M91">
-        <v>1179.42444</v>
+        <v>1192.6764</v>
       </c>
       <c r="N91">
-        <v>-856.02444</v>
+        <v>-869.2764000000001</v>
       </c>
       <c r="O91">
-        <v>-176.34103464</v>
+        <v>-179.0709384</v>
       </c>
       <c r="P91">
-        <v>-679.6834053600001</v>
+        <v>-690.2054616</v>
       </c>
       <c r="Q91">
-        <v>-556.08340536</v>
+        <v>-566.6054616</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2482284100526985</v>
+        <v>0.2684712510579684</v>
       </c>
       <c r="T91">
-        <v>4.675021017383336</v>
+        <v>5.14252311912167</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05648551763095565</v>
+        <v>0.05585790076838948</v>
       </c>
       <c r="W91">
-        <v>0.2224807149426207</v>
+        <v>0.2226287069988138</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.274201541897843</v>
+        <v>0.271154858098978</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2272129614047292</v>
+        <v>0.2291129614047292</v>
       </c>
       <c r="C92">
-        <v>-4249.199486741449</v>
+        <v>-4313.307226452576</v>
       </c>
       <c r="D92">
-        <v>780.7005132585514</v>
+        <v>772.7927735474235</v>
       </c>
       <c r="E92">
-        <v>3999.6</v>
+        <v>4055.8</v>
       </c>
       <c r="F92">
-        <v>5058</v>
+        <v>5114.2</v>
       </c>
       <c r="G92">
         <v>28.1</v>
@@ -8831,37 +8831,37 @@
         <v>323.4</v>
       </c>
       <c r="M92">
-        <v>1192.6764</v>
+        <v>1205.92836</v>
       </c>
       <c r="N92">
-        <v>-869.2764000000001</v>
+        <v>-882.5283600000001</v>
       </c>
       <c r="O92">
-        <v>-179.0709384</v>
+        <v>-181.80084216</v>
       </c>
       <c r="P92">
-        <v>-690.2054616</v>
+        <v>-700.7275178400001</v>
       </c>
       <c r="Q92">
-        <v>-566.6054616</v>
+        <v>-577.1275178400001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2684712510579684</v>
+        <v>0.2932125011755204</v>
       </c>
       <c r="T92">
-        <v>5.14252311912167</v>
+        <v>5.713914576801857</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05585790076838948</v>
+        <v>0.05524407768302256</v>
       </c>
       <c r="W92">
-        <v>0.2226287069988138</v>
+        <v>0.2227734464823433</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.271154858098978</v>
+        <v>0.2681751343836046</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2291129614047292</v>
+        <v>0.2310129614047292</v>
       </c>
       <c r="C93">
-        <v>-4313.307226452576</v>
+        <v>-4377.256377036332</v>
       </c>
       <c r="D93">
-        <v>772.7927735474235</v>
+        <v>765.0436229636687</v>
       </c>
       <c r="E93">
-        <v>4055.8</v>
+        <v>4112</v>
       </c>
       <c r="F93">
-        <v>5114.2</v>
+        <v>5170.400000000001</v>
       </c>
       <c r="G93">
         <v>28.1</v>
@@ -8913,37 +8913,37 @@
         <v>323.4</v>
       </c>
       <c r="M93">
-        <v>1205.92836</v>
+        <v>1219.18032</v>
       </c>
       <c r="N93">
-        <v>-882.5283600000001</v>
+        <v>-895.7803200000002</v>
       </c>
       <c r="O93">
-        <v>-181.80084216</v>
+        <v>-184.53074592</v>
       </c>
       <c r="P93">
-        <v>-700.7275178400001</v>
+        <v>-711.2495740800001</v>
       </c>
       <c r="Q93">
-        <v>-577.1275178400001</v>
+        <v>-587.6495740800001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2932125011755204</v>
+        <v>0.3241390638224605</v>
       </c>
       <c r="T93">
-        <v>5.713914576801857</v>
+        <v>6.428153898902091</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05524407768302256</v>
+        <v>0.05464359857777231</v>
       </c>
       <c r="W93">
-        <v>0.2227734464823433</v>
+        <v>0.2229150394553613</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2681751343836046</v>
+        <v>0.2652601872707393</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2310129614047292</v>
+        <v>0.2329129614047292</v>
       </c>
       <c r="C94">
-        <v>-4377.256377036332</v>
+        <v>-4441.051661868834</v>
       </c>
       <c r="D94">
-        <v>765.0436229636687</v>
+        <v>757.4483381311655</v>
       </c>
       <c r="E94">
-        <v>4112</v>
+        <v>4168.200000000001</v>
       </c>
       <c r="F94">
-        <v>5170.400000000001</v>
+        <v>5226.6</v>
       </c>
       <c r="G94">
         <v>28.1</v>
@@ -8995,37 +8995,37 @@
         <v>323.4</v>
       </c>
       <c r="M94">
-        <v>1219.18032</v>
+        <v>1232.43228</v>
       </c>
       <c r="N94">
-        <v>-895.7803200000002</v>
+        <v>-909.0322800000002</v>
       </c>
       <c r="O94">
-        <v>-184.53074592</v>
+        <v>-187.2606496800001</v>
       </c>
       <c r="P94">
-        <v>-711.2495740800001</v>
+        <v>-721.7716303200002</v>
       </c>
       <c r="Q94">
-        <v>-587.6495740800001</v>
+        <v>-598.1716303200002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3241390638224605</v>
+        <v>0.3639017872256693</v>
       </c>
       <c r="T94">
-        <v>6.428153898902091</v>
+        <v>7.346461598745248</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05464359857777231</v>
+        <v>0.05405603300166723</v>
       </c>
       <c r="W94">
-        <v>0.2229150394553613</v>
+        <v>0.2230535874182069</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2652601872707393</v>
+        <v>0.2624079271925593</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2329129614047292</v>
+        <v>0.2348129614047293</v>
       </c>
       <c r="C95">
-        <v>-4441.051661868834</v>
+        <v>-4504.697618597085</v>
       </c>
       <c r="D95">
-        <v>757.4483381311655</v>
+        <v>750.0023814029151</v>
       </c>
       <c r="E95">
-        <v>4168.200000000001</v>
+        <v>4224.4</v>
       </c>
       <c r="F95">
-        <v>5226.6</v>
+        <v>5282.8</v>
       </c>
       <c r="G95">
         <v>28.1</v>
@@ -9077,37 +9077,37 @@
         <v>323.4</v>
       </c>
       <c r="M95">
-        <v>1232.43228</v>
+        <v>1245.68424</v>
       </c>
       <c r="N95">
-        <v>-909.0322800000002</v>
+        <v>-922.2842400000001</v>
       </c>
       <c r="O95">
-        <v>-187.2606496800001</v>
+        <v>-189.99055344</v>
       </c>
       <c r="P95">
-        <v>-721.7716303200002</v>
+        <v>-732.29368656</v>
       </c>
       <c r="Q95">
-        <v>-598.1716303200002</v>
+        <v>-608.6936865599999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3639017872256693</v>
+        <v>0.4169187517632809</v>
       </c>
       <c r="T95">
-        <v>7.346461598745248</v>
+        <v>8.570871865202792</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05405603300166723</v>
+        <v>0.05348096882079843</v>
       </c>
       <c r="W95">
-        <v>0.2230535874182069</v>
+        <v>0.2231891875520557</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2624079271925593</v>
+        <v>0.2596163534990216</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2348129614047293</v>
+        <v>0.2367129614047292</v>
       </c>
       <c r="C96">
-        <v>-4504.697618597085</v>
+        <v>-4568.198608178967</v>
       </c>
       <c r="D96">
-        <v>750.0023814029151</v>
+        <v>742.7013918210326</v>
       </c>
       <c r="E96">
-        <v>4224.4</v>
+        <v>4280.6</v>
       </c>
       <c r="F96">
-        <v>5282.8</v>
+        <v>5339</v>
       </c>
       <c r="G96">
         <v>28.1</v>
@@ -9159,37 +9159,37 @@
         <v>323.4</v>
       </c>
       <c r="M96">
-        <v>1245.68424</v>
+        <v>1258.9362</v>
       </c>
       <c r="N96">
-        <v>-922.2842400000001</v>
+        <v>-935.5362000000001</v>
       </c>
       <c r="O96">
-        <v>-189.99055344</v>
+        <v>-192.7204572</v>
       </c>
       <c r="P96">
-        <v>-732.29368656</v>
+        <v>-742.8157428000001</v>
       </c>
       <c r="Q96">
-        <v>-608.6936865599999</v>
+        <v>-619.2157428</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4169187517632809</v>
+        <v>0.4911425021159372</v>
       </c>
       <c r="T96">
-        <v>8.570871865202792</v>
+        <v>10.28504623824335</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05348096882079843</v>
+        <v>0.05291801125426372</v>
       </c>
       <c r="W96">
-        <v>0.2231891875520557</v>
+        <v>0.2233219329462446</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2596163534990216</v>
+        <v>0.2568835497779792</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2367129614047292</v>
+        <v>0.2386129614047292</v>
       </c>
       <c r="C97">
-        <v>-4568.198608178967</v>
+        <v>-4631.558823400359</v>
       </c>
       <c r="D97">
-        <v>742.7013918210326</v>
+        <v>735.541176599642</v>
       </c>
       <c r="E97">
-        <v>4280.6</v>
+        <v>4336.800000000001</v>
       </c>
       <c r="F97">
-        <v>5339</v>
+        <v>5395.200000000001</v>
       </c>
       <c r="G97">
         <v>28.1</v>
@@ -9241,37 +9241,37 @@
         <v>323.4</v>
       </c>
       <c r="M97">
-        <v>1258.9362</v>
+        <v>1272.18816</v>
       </c>
       <c r="N97">
-        <v>-935.5362000000001</v>
+        <v>-948.7881600000002</v>
       </c>
       <c r="O97">
-        <v>-192.7204572</v>
+        <v>-195.45036096</v>
       </c>
       <c r="P97">
-        <v>-742.8157428000001</v>
+        <v>-753.3377990400002</v>
       </c>
       <c r="Q97">
-        <v>-619.2157428</v>
+        <v>-629.7377990400001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4911425021159372</v>
+        <v>0.6024781276449218</v>
       </c>
       <c r="T97">
-        <v>10.28504623824335</v>
+        <v>12.8563077978042</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05291801125426372</v>
+        <v>0.05236678197036513</v>
       </c>
       <c r="W97">
-        <v>0.2233219329462446</v>
+        <v>0.2234519128113879</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2568835497779792</v>
+        <v>0.2542076794677919</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2386129614047292</v>
+        <v>0.2405129614047292</v>
       </c>
       <c r="C98">
-        <v>-4631.558823400358</v>
+        <v>-4694.782296904249</v>
       </c>
       <c r="D98">
-        <v>735.541176599642</v>
+        <v>728.5177030957506</v>
       </c>
       <c r="E98">
-        <v>4336.799999999999</v>
+        <v>4393</v>
       </c>
       <c r="F98">
-        <v>5395.2</v>
+        <v>5451.4</v>
       </c>
       <c r="G98">
         <v>28.1</v>
@@ -9323,37 +9323,37 @@
         <v>323.4</v>
       </c>
       <c r="M98">
-        <v>1272.18816</v>
+        <v>1285.44012</v>
       </c>
       <c r="N98">
-        <v>-948.7881599999999</v>
+        <v>-962.04012</v>
       </c>
       <c r="O98">
-        <v>-195.45036096</v>
+        <v>-198.18026472</v>
       </c>
       <c r="P98">
-        <v>-753.3377990399999</v>
+        <v>-763.8598552799999</v>
       </c>
       <c r="Q98">
-        <v>-629.7377990399999</v>
+        <v>-640.2598552799999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6024781276449204</v>
+        <v>0.7880375035265605</v>
       </c>
       <c r="T98">
-        <v>12.85630779780417</v>
+        <v>17.14174373040555</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05236678197036514</v>
+        <v>0.05182691823871189</v>
       </c>
       <c r="W98">
-        <v>0.2234519128113879</v>
+        <v>0.2235792126793117</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2542076794677919</v>
+        <v>0.2515869817413199</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2405129614047292</v>
+        <v>0.2424129614047292</v>
       </c>
       <c r="C99">
-        <v>-4694.782296904249</v>
+        <v>-4757.872908764234</v>
       </c>
       <c r="D99">
-        <v>728.5177030957506</v>
+        <v>721.6270912357655</v>
       </c>
       <c r="E99">
-        <v>4393</v>
+        <v>4449.199999999999</v>
       </c>
       <c r="F99">
-        <v>5451.4</v>
+        <v>5507.599999999999</v>
       </c>
       <c r="G99">
         <v>28.1</v>
@@ -9405,37 +9405,37 @@
         <v>323.4</v>
       </c>
       <c r="M99">
-        <v>1285.44012</v>
+        <v>1298.69208</v>
       </c>
       <c r="N99">
-        <v>-962.04012</v>
+        <v>-975.2920800000001</v>
       </c>
       <c r="O99">
-        <v>-198.18026472</v>
+        <v>-200.91016848</v>
       </c>
       <c r="P99">
-        <v>-763.8598552799999</v>
+        <v>-774.38191152</v>
       </c>
       <c r="Q99">
-        <v>-640.2598552799999</v>
+        <v>-650.78191152</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7880375035265605</v>
+        <v>1.159156255289841</v>
       </c>
       <c r="T99">
-        <v>17.14174373040555</v>
+        <v>25.71261559560833</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05182691823871189</v>
+        <v>0.05129807213423523</v>
       </c>
       <c r="W99">
-        <v>0.2235792126793117</v>
+        <v>0.2237039145907473</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2515869817413199</v>
+        <v>0.2490197676419186</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2424129614047292</v>
+        <v>0.2443129614047292</v>
       </c>
       <c r="C100">
-        <v>-4757.872908764234</v>
+        <v>-4820.834393632209</v>
       </c>
       <c r="D100">
-        <v>721.6270912357655</v>
+        <v>714.8656063677911</v>
       </c>
       <c r="E100">
-        <v>4449.199999999999</v>
+        <v>4505.4</v>
       </c>
       <c r="F100">
-        <v>5507.599999999999</v>
+        <v>5563.8</v>
       </c>
       <c r="G100">
         <v>28.1</v>
@@ -9487,37 +9487,37 @@
         <v>323.4</v>
       </c>
       <c r="M100">
-        <v>1298.69208</v>
+        <v>1311.94404</v>
       </c>
       <c r="N100">
-        <v>-975.2920800000001</v>
+        <v>-988.5440400000001</v>
       </c>
       <c r="O100">
-        <v>-200.91016848</v>
+        <v>-203.6400722400001</v>
       </c>
       <c r="P100">
-        <v>-774.38191152</v>
+        <v>-784.9039677600001</v>
       </c>
       <c r="Q100">
-        <v>-650.78191152</v>
+        <v>-661.3039677600001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.159156255289841</v>
+        <v>2.272512510579681</v>
       </c>
       <c r="T100">
-        <v>25.71261559560833</v>
+        <v>51.42523119121665</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05129807213423523</v>
+        <v>0.05077990978944498</v>
       </c>
       <c r="W100">
-        <v>0.2237039145907473</v>
+        <v>0.2238260972716489</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2490197676419186</v>
+        <v>0.2465044164536164</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2443129614047292</v>
-      </c>
-      <c r="C101">
-        <v>-4820.834393632209</v>
-      </c>
-      <c r="D101">
-        <v>714.8656063677911</v>
-      </c>
-      <c r="E101">
-        <v>4505.4</v>
-      </c>
-      <c r="F101">
-        <v>5563.8</v>
-      </c>
-      <c r="G101">
-        <v>28.1</v>
-      </c>
-      <c r="H101">
-        <v>4561.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>447</v>
-      </c>
-      <c r="K101">
-        <v>123.6</v>
-      </c>
-      <c r="L101">
-        <v>323.4</v>
-      </c>
-      <c r="M101">
-        <v>1311.94404</v>
-      </c>
-      <c r="N101">
-        <v>-988.5440400000001</v>
-      </c>
-      <c r="O101">
-        <v>-203.6400722400001</v>
-      </c>
-      <c r="P101">
-        <v>-784.9039677600001</v>
-      </c>
-      <c r="Q101">
-        <v>-661.3039677600001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.272512510579681</v>
-      </c>
-      <c r="T101">
-        <v>51.42523119121665</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05077990978944498</v>
-      </c>
-      <c r="W101">
-        <v>0.2238260972716489</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2465044164536164</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
